--- a/TCPL Rulesets - GL1 (1).xlsx
+++ b/TCPL Rulesets - GL1 (1).xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29922"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://eyindia.sharepoint.com/sites/TCPLProject/Shared Documents/TCPL/Functional/Rulesets/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SEM-8\Data Rules Set Check\Data_rulesets_check\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E547BCD7-5537-40FF-A02D-5A3BA482CC94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9312E81D-AAD5-4E34-8FC0-047236D466A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="906" firstSheet="12" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="906" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data Availability backup" sheetId="89" state="hidden" r:id="rId1"/>
@@ -29,9 +29,6 @@
     <sheet name="Calendar" sheetId="54" r:id="rId14"/>
     <sheet name="CalendarDate" sheetId="63" r:id="rId15"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId16"/>
-  </externalReferences>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">Customer!$B$6:$C$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Data Availability backup2'!$B$23:$AH$101</definedName>
@@ -78,21 +75,21 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <metadataTypes count="1">
     <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
   </metadataTypes>
   <futureMetadata name="XLRICHVALUE" count="2">
     <bk>
       <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+        <ext xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
           <xlrd:rvb i="0"/>
         </ext>
       </extLst>
     </bk>
     <bk>
       <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+        <ext xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
           <xlrd:rvb i="1"/>
         </ext>
       </extLst>
@@ -2544,7 +2541,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="21">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3548,116 +3545,116 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -3815,6 +3812,15 @@
     </dxf>
     <dxf>
       <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
@@ -3822,15 +3828,6 @@
     </dxf>
     <dxf>
       <border outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
@@ -4004,6 +4001,15 @@
     </dxf>
     <dxf>
       <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
@@ -4011,15 +4017,6 @@
     </dxf>
     <dxf>
       <border outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
@@ -4126,13 +4123,6 @@
     </dxf>
     <dxf>
       <border outline="0">
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
@@ -4149,6 +4139,13 @@
     </dxf>
     <dxf>
       <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -4330,13 +4327,6 @@
     </dxf>
     <dxf>
       <border outline="0">
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
@@ -4353,6 +4343,13 @@
     </dxf>
     <dxf>
       <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -4510,13 +4507,6 @@
     </dxf>
     <dxf>
       <border outline="0">
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
@@ -4533,6 +4523,13 @@
     </dxf>
     <dxf>
       <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -4687,13 +4684,6 @@
     </dxf>
     <dxf>
       <border outline="0">
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
@@ -4707,6 +4697,13 @@
     </dxf>
     <dxf>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -4800,13 +4797,6 @@
     </dxf>
     <dxf>
       <border outline="0">
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
@@ -4823,6 +4813,13 @@
     </dxf>
     <dxf>
       <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -5135,13 +5132,6 @@
     </dxf>
     <dxf>
       <border outline="0">
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
@@ -5152,6 +5142,13 @@
     </dxf>
     <dxf>
       <alignment horizontal="general" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -5305,19 +5302,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="Summary "/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
 <file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
 <rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
   <global>
@@ -5388,7 +5372,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{6CEB2B68-6D66-45C8-B591-6B731C97038B}" name="Table2" displayName="Table2" ref="B6:C11" totalsRowShown="0" headerRowDxfId="81" dataDxfId="80" headerRowBorderDxfId="78" tableBorderDxfId="79">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{6CEB2B68-6D66-45C8-B591-6B731C97038B}" name="Table2" displayName="Table2" ref="B6:C11" totalsRowShown="0" headerRowDxfId="81" dataDxfId="79" headerRowBorderDxfId="80" tableBorderDxfId="78">
   <autoFilter ref="B6:C11" xr:uid="{6CEB2B68-6D66-45C8-B591-6B731C97038B}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{DFA72B13-79A0-4E6B-BFE8-9C951CC20DB7}" name="Field Name " dataDxfId="77"/>
@@ -5416,7 +5400,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="21" xr:uid="{CEF90194-F366-4143-BE58-1D69A4E9DB9E}" name="Table21" displayName="Table21" ref="B7:C11" totalsRowShown="0" headerRowDxfId="64" dataDxfId="63" headerRowBorderDxfId="61" tableBorderDxfId="62" totalsRowBorderDxfId="60">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="21" xr:uid="{CEF90194-F366-4143-BE58-1D69A4E9DB9E}" name="Table21" displayName="Table21" ref="B7:C11" totalsRowShown="0" headerRowDxfId="64" dataDxfId="62" headerRowBorderDxfId="63" tableBorderDxfId="61" totalsRowBorderDxfId="60">
   <autoFilter ref="B7:C11" xr:uid="{CEF90194-F366-4143-BE58-1D69A4E9DB9E}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{A784E209-C2E4-4FA2-8B12-8CBA6AAA6ED8}" name="Field Name " dataDxfId="59"/>
@@ -5427,7 +5411,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="23" xr:uid="{10F78BC5-A04E-43AD-B328-A5E2F4154FDB}" name="Table23" displayName="Table23" ref="B7:F21" totalsRowShown="0" headerRowDxfId="57" dataDxfId="56" headerRowBorderDxfId="54" tableBorderDxfId="55" totalsRowBorderDxfId="53">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="23" xr:uid="{10F78BC5-A04E-43AD-B328-A5E2F4154FDB}" name="Table23" displayName="Table23" ref="B7:F21" totalsRowShown="0" headerRowDxfId="57" dataDxfId="55" headerRowBorderDxfId="56" tableBorderDxfId="54" totalsRowBorderDxfId="53">
   <autoFilter ref="B7:F21" xr:uid="{10F78BC5-A04E-43AD-B328-A5E2F4154FDB}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{8D984732-2238-4561-BDF5-09F2C498D501}" name="Field Name " dataDxfId="52"/>
@@ -5441,7 +5425,7 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{34CFE5C1-7306-4776-829D-846D8B15B850}" name="Table8" displayName="Table8" ref="B7:F11" totalsRowShown="0" headerRowDxfId="47" dataDxfId="46" headerRowBorderDxfId="44" tableBorderDxfId="45">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{34CFE5C1-7306-4776-829D-846D8B15B850}" name="Table8" displayName="Table8" ref="B7:F11" totalsRowShown="0" headerRowDxfId="47" dataDxfId="45" headerRowBorderDxfId="46" tableBorderDxfId="44">
   <autoFilter ref="B7:F11" xr:uid="{34CFE5C1-7306-4776-829D-846D8B15B850}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{A612CD54-CAA0-4BAC-9ACA-9913FF3D1EE3}" name="Field Name " dataDxfId="43"/>
@@ -5455,7 +5439,7 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="29" xr:uid="{5EEE0AEB-3FE4-49DA-A063-6D602A23AC80}" name="Table830" displayName="Table830" ref="B7:F11" totalsRowShown="0" headerRowDxfId="38" dataDxfId="37" headerRowBorderDxfId="35" tableBorderDxfId="36">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="29" xr:uid="{5EEE0AEB-3FE4-49DA-A063-6D602A23AC80}" name="Table830" displayName="Table830" ref="B7:F11" totalsRowShown="0" headerRowDxfId="38" dataDxfId="36" headerRowBorderDxfId="37" tableBorderDxfId="35">
   <autoFilter ref="B7:F11" xr:uid="{34CFE5C1-7306-4776-829D-846D8B15B850}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{ECAA1F64-929B-43AB-AF81-1AB45D7E86D2}" name="Field Name " dataDxfId="34"/>
@@ -5469,7 +5453,7 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{F5C58C9C-57EA-46DF-9554-30E1673CA60C}" name="Table11" displayName="Table11" ref="B7:E32" totalsRowShown="0" headerRowDxfId="29" dataDxfId="28" headerRowBorderDxfId="26" tableBorderDxfId="27">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{F5C58C9C-57EA-46DF-9554-30E1673CA60C}" name="Table11" displayName="Table11" ref="B7:E32" totalsRowShown="0" headerRowDxfId="29" dataDxfId="27" headerRowBorderDxfId="28" tableBorderDxfId="26">
   <autoFilter ref="B7:E32" xr:uid="{F5C58C9C-57EA-46DF-9554-30E1673CA60C}"/>
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{109BBFCB-488C-4463-A4AB-249CB1C197A0}" name="Field Name " dataDxfId="25"/>
@@ -5482,7 +5466,7 @@
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="20" xr:uid="{2475EE39-6180-45BC-B447-CE8E43C8BDF8}" name="Table20" displayName="Table20" ref="A4:G7" totalsRowShown="0" headerRowDxfId="21" headerRowBorderDxfId="19" tableBorderDxfId="20" totalsRowBorderDxfId="18">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="20" xr:uid="{2475EE39-6180-45BC-B447-CE8E43C8BDF8}" name="Table20" displayName="Table20" ref="A4:G7" totalsRowShown="0" headerRowDxfId="21" headerRowBorderDxfId="20" tableBorderDxfId="19" totalsRowBorderDxfId="18">
   <autoFilter ref="A4:G7" xr:uid="{2475EE39-6180-45BC-B447-CE8E43C8BDF8}"/>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{0580DE81-FDE5-45D1-AA4B-C4AAE0CD9A1B}" name="Field Name " dataDxfId="17"/>
@@ -5498,7 +5482,7 @@
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{03DF2551-0BD6-4832-A349-1F6C8164FB2C}" name="Table10" displayName="Table10" ref="A4:G7" totalsRowShown="0" headerRowDxfId="10" headerRowBorderDxfId="8" tableBorderDxfId="9" totalsRowBorderDxfId="7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{03DF2551-0BD6-4832-A349-1F6C8164FB2C}" name="Table10" displayName="Table10" ref="A4:G7" totalsRowShown="0" headerRowDxfId="10" headerRowBorderDxfId="9" tableBorderDxfId="8" totalsRowBorderDxfId="7">
   <autoFilter ref="A4:G7" xr:uid="{03DF2551-0BD6-4832-A349-1F6C8164FB2C}"/>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{30A74F40-2D51-40B2-A327-3D3CA84680AE}" name="Field Name " dataDxfId="6"/>
@@ -5811,58 +5795,58 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5006AC66-8A03-4CB5-B6C7-EEA6414481EC}">
   <dimension ref="B2:M67"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="22.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="24.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="9" width="16.140625" customWidth="1"/>
-    <col min="10" max="10" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.81640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.81640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="24.453125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.1796875" bestFit="1" customWidth="1"/>
+    <col min="7" max="9" width="16.1796875" customWidth="1"/>
+    <col min="10" max="10" width="9.54296875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.54296875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:13">
-      <c r="B2" s="172" t="s">
+    <row r="2" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B2" s="173" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="174" t="s">
+      <c r="C2" s="170" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="172" t="s">
+      <c r="D2" s="173" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="174" t="s">
+      <c r="E2" s="170" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="174" t="s">
+      <c r="F2" s="170" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="174" t="s">
+      <c r="G2" s="170" t="s">
         <v>5</v>
       </c>
-      <c r="H2" s="174" t="s">
+      <c r="H2" s="170" t="s">
         <v>6</v>
       </c>
       <c r="I2" s="77"/>
-      <c r="J2" s="171" t="s">
+      <c r="J2" s="172" t="s">
         <v>7</v>
       </c>
-      <c r="K2" s="171"/>
-      <c r="L2" s="171"/>
-      <c r="M2" s="171"/>
-    </row>
-    <row r="3" spans="2:13">
-      <c r="B3" s="172"/>
-      <c r="C3" s="175"/>
-      <c r="D3" s="172"/>
-      <c r="E3" s="175"/>
-      <c r="F3" s="175"/>
-      <c r="G3" s="175"/>
-      <c r="H3" s="175"/>
+      <c r="K2" s="172"/>
+      <c r="L2" s="172"/>
+      <c r="M2" s="172"/>
+    </row>
+    <row r="3" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B3" s="173"/>
+      <c r="C3" s="171"/>
+      <c r="D3" s="173"/>
+      <c r="E3" s="171"/>
+      <c r="F3" s="171"/>
+      <c r="G3" s="171"/>
+      <c r="H3" s="171"/>
       <c r="I3" s="78"/>
       <c r="J3" s="4" t="s">
         <v>8</v>
@@ -5877,8 +5861,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="2:13">
-      <c r="B4" s="173">
+    <row r="4" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B4" s="169">
         <v>1</v>
       </c>
       <c r="C4" s="6" t="s">
@@ -5901,8 +5885,8 @@
       <c r="L4" s="3"/>
       <c r="M4" s="3"/>
     </row>
-    <row r="5" spans="2:13">
-      <c r="B5" s="173"/>
+    <row r="5" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B5" s="169"/>
       <c r="C5" s="6" t="s">
         <v>12</v>
       </c>
@@ -5919,8 +5903,8 @@
       <c r="L5" s="3"/>
       <c r="M5" s="3"/>
     </row>
-    <row r="6" spans="2:13">
-      <c r="B6" s="173"/>
+    <row r="6" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B6" s="169"/>
       <c r="C6" s="6" t="s">
         <v>12</v>
       </c>
@@ -5941,8 +5925,8 @@
       <c r="L6" s="3"/>
       <c r="M6" s="3"/>
     </row>
-    <row r="7" spans="2:13">
-      <c r="B7" s="173"/>
+    <row r="7" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B7" s="169"/>
       <c r="C7" s="6" t="s">
         <v>12</v>
       </c>
@@ -5963,8 +5947,8 @@
       <c r="L7" s="3"/>
       <c r="M7" s="3"/>
     </row>
-    <row r="8" spans="2:13">
-      <c r="B8" s="173"/>
+    <row r="8" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B8" s="169"/>
       <c r="C8" s="6" t="s">
         <v>12</v>
       </c>
@@ -5985,8 +5969,8 @@
       <c r="L8" s="3"/>
       <c r="M8" s="3"/>
     </row>
-    <row r="9" spans="2:13">
-      <c r="B9" s="173"/>
+    <row r="9" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B9" s="169"/>
       <c r="C9" s="6" t="s">
         <v>12</v>
       </c>
@@ -6007,8 +5991,8 @@
       <c r="L9" s="3"/>
       <c r="M9" s="3"/>
     </row>
-    <row r="10" spans="2:13">
-      <c r="B10" s="173"/>
+    <row r="10" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B10" s="169"/>
       <c r="C10" s="6" t="s">
         <v>12</v>
       </c>
@@ -6029,8 +6013,8 @@
       <c r="L10" s="3"/>
       <c r="M10" s="3"/>
     </row>
-    <row r="11" spans="2:13">
-      <c r="B11" s="173"/>
+    <row r="11" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B11" s="169"/>
       <c r="C11" s="6" t="s">
         <v>12</v>
       </c>
@@ -6051,8 +6035,8 @@
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
     </row>
-    <row r="12" spans="2:13">
-      <c r="B12" s="173">
+    <row r="12" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B12" s="169">
         <v>2</v>
       </c>
       <c r="C12" s="6" t="s">
@@ -6075,8 +6059,8 @@
       <c r="L12" s="3"/>
       <c r="M12" s="3"/>
     </row>
-    <row r="13" spans="2:13">
-      <c r="B13" s="173"/>
+    <row r="13" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B13" s="169"/>
       <c r="C13" s="6" t="s">
         <v>31</v>
       </c>
@@ -6097,8 +6081,8 @@
       <c r="L13" s="3"/>
       <c r="M13" s="3"/>
     </row>
-    <row r="14" spans="2:13">
-      <c r="B14" s="173"/>
+    <row r="14" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B14" s="169"/>
       <c r="C14" s="6" t="s">
         <v>31</v>
       </c>
@@ -6119,8 +6103,8 @@
       <c r="L14" s="3"/>
       <c r="M14" s="3"/>
     </row>
-    <row r="15" spans="2:13">
-      <c r="B15" s="173"/>
+    <row r="15" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B15" s="169"/>
       <c r="C15" s="6" t="s">
         <v>31</v>
       </c>
@@ -6141,8 +6125,8 @@
       <c r="L15" s="3"/>
       <c r="M15" s="3"/>
     </row>
-    <row r="16" spans="2:13">
-      <c r="B16" s="173"/>
+    <row r="16" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B16" s="169"/>
       <c r="C16" s="6" t="s">
         <v>31</v>
       </c>
@@ -6163,8 +6147,8 @@
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
     </row>
-    <row r="17" spans="2:13">
-      <c r="B17" s="173"/>
+    <row r="17" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B17" s="169"/>
       <c r="C17" s="6" t="s">
         <v>31</v>
       </c>
@@ -6185,8 +6169,8 @@
       <c r="L17" s="3"/>
       <c r="M17" s="3"/>
     </row>
-    <row r="18" spans="2:13">
-      <c r="B18" s="173"/>
+    <row r="18" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B18" s="169"/>
       <c r="C18" s="6" t="s">
         <v>31</v>
       </c>
@@ -6207,8 +6191,8 @@
       <c r="L18" s="3"/>
       <c r="M18" s="3"/>
     </row>
-    <row r="19" spans="2:13">
-      <c r="B19" s="173"/>
+    <row r="19" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B19" s="169"/>
       <c r="C19" s="6" t="s">
         <v>31</v>
       </c>
@@ -6225,8 +6209,8 @@
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
     </row>
-    <row r="20" spans="2:13">
-      <c r="B20" s="173"/>
+    <row r="20" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B20" s="169"/>
       <c r="C20" s="6" t="s">
         <v>31</v>
       </c>
@@ -6243,8 +6227,8 @@
       <c r="L20" s="3"/>
       <c r="M20" s="3"/>
     </row>
-    <row r="21" spans="2:13">
-      <c r="B21" s="173"/>
+    <row r="21" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B21" s="169"/>
       <c r="C21" s="6" t="s">
         <v>31</v>
       </c>
@@ -6261,8 +6245,8 @@
       <c r="L21" s="3"/>
       <c r="M21" s="3"/>
     </row>
-    <row r="22" spans="2:13">
-      <c r="B22" s="173"/>
+    <row r="22" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B22" s="169"/>
       <c r="C22" s="6" t="s">
         <v>31</v>
       </c>
@@ -6283,8 +6267,8 @@
       <c r="L22" s="3"/>
       <c r="M22" s="3"/>
     </row>
-    <row r="23" spans="2:13">
-      <c r="B23" s="173"/>
+    <row r="23" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B23" s="169"/>
       <c r="C23" s="6" t="s">
         <v>31</v>
       </c>
@@ -6301,8 +6285,8 @@
       <c r="L23" s="3"/>
       <c r="M23" s="3"/>
     </row>
-    <row r="24" spans="2:13">
-      <c r="B24" s="173">
+    <row r="24" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B24" s="169">
         <v>3</v>
       </c>
       <c r="C24" s="6" t="s">
@@ -6321,8 +6305,8 @@
       <c r="L24" s="3"/>
       <c r="M24" s="3"/>
     </row>
-    <row r="25" spans="2:13">
-      <c r="B25" s="173"/>
+    <row r="25" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B25" s="169"/>
       <c r="C25" s="6" t="s">
         <v>57</v>
       </c>
@@ -6339,8 +6323,8 @@
       <c r="L25" s="3"/>
       <c r="M25" s="3"/>
     </row>
-    <row r="26" spans="2:13">
-      <c r="B26" s="173">
+    <row r="26" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B26" s="169">
         <v>4</v>
       </c>
       <c r="C26" s="6" t="s">
@@ -6363,8 +6347,8 @@
       <c r="L26" s="3"/>
       <c r="M26" s="3"/>
     </row>
-    <row r="27" spans="2:13">
-      <c r="B27" s="173"/>
+    <row r="27" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B27" s="169"/>
       <c r="C27" s="6" t="s">
         <v>60</v>
       </c>
@@ -6385,8 +6369,8 @@
       <c r="L27" s="3"/>
       <c r="M27" s="3"/>
     </row>
-    <row r="28" spans="2:13">
-      <c r="B28" s="173"/>
+    <row r="28" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B28" s="169"/>
       <c r="C28" s="6" t="s">
         <v>60</v>
       </c>
@@ -6407,8 +6391,8 @@
       <c r="L28" s="3"/>
       <c r="M28" s="3"/>
     </row>
-    <row r="29" spans="2:13">
-      <c r="B29" s="173"/>
+    <row r="29" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B29" s="169"/>
       <c r="C29" s="6" t="s">
         <v>60</v>
       </c>
@@ -6429,8 +6413,8 @@
       <c r="L29" s="3"/>
       <c r="M29" s="3"/>
     </row>
-    <row r="30" spans="2:13">
-      <c r="B30" s="173"/>
+    <row r="30" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B30" s="169"/>
       <c r="C30" s="6" t="s">
         <v>60</v>
       </c>
@@ -6451,8 +6435,8 @@
       <c r="L30" s="3"/>
       <c r="M30" s="3"/>
     </row>
-    <row r="31" spans="2:13">
-      <c r="B31" s="173"/>
+    <row r="31" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B31" s="169"/>
       <c r="C31" s="6" t="s">
         <v>60</v>
       </c>
@@ -6473,11 +6457,11 @@
       <c r="L31" s="3"/>
       <c r="M31" s="3"/>
     </row>
-    <row r="32" spans="2:13">
-      <c r="B32" s="173">
+    <row r="32" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B32" s="169">
         <v>5</v>
       </c>
-      <c r="C32" s="173" t="s">
+      <c r="C32" s="169" t="s">
         <v>73</v>
       </c>
       <c r="D32" s="3" t="s">
@@ -6493,9 +6477,9 @@
       <c r="L32" s="3"/>
       <c r="M32" s="3"/>
     </row>
-    <row r="33" spans="2:13">
-      <c r="B33" s="173"/>
-      <c r="C33" s="173"/>
+    <row r="33" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B33" s="169"/>
+      <c r="C33" s="169"/>
       <c r="D33" s="3" t="s">
         <v>75</v>
       </c>
@@ -6509,9 +6493,9 @@
       <c r="L33" s="3"/>
       <c r="M33" s="3"/>
     </row>
-    <row r="34" spans="2:13">
-      <c r="B34" s="173"/>
-      <c r="C34" s="173"/>
+    <row r="34" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B34" s="169"/>
+      <c r="C34" s="169"/>
       <c r="D34" s="57" t="s">
         <v>76</v>
       </c>
@@ -6529,9 +6513,9 @@
       <c r="L34" s="3"/>
       <c r="M34" s="3"/>
     </row>
-    <row r="35" spans="2:13" ht="15.6">
-      <c r="B35" s="173"/>
-      <c r="C35" s="173"/>
+    <row r="35" spans="2:13" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B35" s="169"/>
+      <c r="C35" s="169"/>
       <c r="D35" s="57" t="s">
         <v>78</v>
       </c>
@@ -6549,9 +6533,9 @@
       <c r="L35" s="3"/>
       <c r="M35" s="3"/>
     </row>
-    <row r="36" spans="2:13">
-      <c r="B36" s="173"/>
-      <c r="C36" s="173"/>
+    <row r="36" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B36" s="169"/>
+      <c r="C36" s="169"/>
       <c r="D36" s="3" t="s">
         <v>79</v>
       </c>
@@ -6569,9 +6553,9 @@
       <c r="L36" s="3"/>
       <c r="M36" s="3"/>
     </row>
-    <row r="37" spans="2:13">
-      <c r="B37" s="173"/>
-      <c r="C37" s="173"/>
+    <row r="37" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B37" s="169"/>
+      <c r="C37" s="169"/>
       <c r="D37" s="3" t="s">
         <v>81</v>
       </c>
@@ -6589,9 +6573,9 @@
       <c r="L37" s="3"/>
       <c r="M37" s="3"/>
     </row>
-    <row r="38" spans="2:13">
-      <c r="B38" s="173"/>
-      <c r="C38" s="173"/>
+    <row r="38" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B38" s="169"/>
+      <c r="C38" s="169"/>
       <c r="D38" s="3" t="s">
         <v>82</v>
       </c>
@@ -6609,9 +6593,9 @@
       <c r="L38" s="3"/>
       <c r="M38" s="3"/>
     </row>
-    <row r="39" spans="2:13">
-      <c r="B39" s="173"/>
-      <c r="C39" s="173"/>
+    <row r="39" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B39" s="169"/>
+      <c r="C39" s="169"/>
       <c r="D39" s="3" t="s">
         <v>84</v>
       </c>
@@ -6629,9 +6613,9 @@
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
     </row>
-    <row r="40" spans="2:13">
-      <c r="B40" s="173"/>
-      <c r="C40" s="173"/>
+    <row r="40" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B40" s="169"/>
+      <c r="C40" s="169"/>
       <c r="D40" s="3" t="s">
         <v>85</v>
       </c>
@@ -6645,9 +6629,9 @@
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
     </row>
-    <row r="41" spans="2:13">
-      <c r="B41" s="173"/>
-      <c r="C41" s="173"/>
+    <row r="41" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B41" s="169"/>
+      <c r="C41" s="169"/>
       <c r="D41" s="3" t="s">
         <v>86</v>
       </c>
@@ -6661,9 +6645,9 @@
       <c r="L41" s="3"/>
       <c r="M41" s="3"/>
     </row>
-    <row r="42" spans="2:13">
-      <c r="B42" s="173"/>
-      <c r="C42" s="173"/>
+    <row r="42" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B42" s="169"/>
+      <c r="C42" s="169"/>
       <c r="D42" s="3" t="s">
         <v>87</v>
       </c>
@@ -6681,9 +6665,9 @@
       <c r="L42" s="3"/>
       <c r="M42" s="3"/>
     </row>
-    <row r="43" spans="2:13">
-      <c r="B43" s="173"/>
-      <c r="C43" s="173"/>
+    <row r="43" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B43" s="169"/>
+      <c r="C43" s="169"/>
       <c r="D43" s="3" t="s">
         <v>89</v>
       </c>
@@ -6701,9 +6685,9 @@
       <c r="L43" s="3"/>
       <c r="M43" s="3"/>
     </row>
-    <row r="44" spans="2:13">
-      <c r="B44" s="173"/>
-      <c r="C44" s="173"/>
+    <row r="44" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B44" s="169"/>
+      <c r="C44" s="169"/>
       <c r="D44" s="3" t="s">
         <v>90</v>
       </c>
@@ -6717,9 +6701,9 @@
       <c r="L44" s="3"/>
       <c r="M44" s="3"/>
     </row>
-    <row r="45" spans="2:13">
-      <c r="B45" s="173"/>
-      <c r="C45" s="173"/>
+    <row r="45" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B45" s="169"/>
+      <c r="C45" s="169"/>
       <c r="D45" s="3" t="s">
         <v>91</v>
       </c>
@@ -6733,9 +6717,9 @@
       <c r="L45" s="3"/>
       <c r="M45" s="3"/>
     </row>
-    <row r="46" spans="2:13">
-      <c r="B46" s="173"/>
-      <c r="C46" s="173"/>
+    <row r="46" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B46" s="169"/>
+      <c r="C46" s="169"/>
       <c r="D46" s="3" t="s">
         <v>92</v>
       </c>
@@ -6753,9 +6737,9 @@
       <c r="L46" s="3"/>
       <c r="M46" s="3"/>
     </row>
-    <row r="47" spans="2:13">
-      <c r="B47" s="173"/>
-      <c r="C47" s="173"/>
+    <row r="47" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B47" s="169"/>
+      <c r="C47" s="169"/>
       <c r="D47" s="3" t="s">
         <v>93</v>
       </c>
@@ -6773,9 +6757,9 @@
       <c r="L47" s="3"/>
       <c r="M47" s="3"/>
     </row>
-    <row r="48" spans="2:13">
-      <c r="B48" s="173"/>
-      <c r="C48" s="173"/>
+    <row r="48" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B48" s="169"/>
+      <c r="C48" s="169"/>
       <c r="D48" s="3" t="s">
         <v>94</v>
       </c>
@@ -6789,9 +6773,9 @@
       <c r="L48" s="3"/>
       <c r="M48" s="3"/>
     </row>
-    <row r="49" spans="2:13">
-      <c r="B49" s="173"/>
-      <c r="C49" s="173"/>
+    <row r="49" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B49" s="169"/>
+      <c r="C49" s="169"/>
       <c r="D49" s="3" t="s">
         <v>95</v>
       </c>
@@ -6805,11 +6789,11 @@
       <c r="L49" s="3"/>
       <c r="M49" s="3"/>
     </row>
-    <row r="50" spans="2:13">
-      <c r="B50" s="173">
+    <row r="50" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B50" s="169">
         <v>6</v>
       </c>
-      <c r="C50" s="173" t="s">
+      <c r="C50" s="169" t="s">
         <v>96</v>
       </c>
       <c r="D50" s="3" t="s">
@@ -6829,9 +6813,9 @@
       <c r="L50" s="3"/>
       <c r="M50" s="3"/>
     </row>
-    <row r="51" spans="2:13">
-      <c r="B51" s="173"/>
-      <c r="C51" s="173"/>
+    <row r="51" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B51" s="169"/>
+      <c r="C51" s="169"/>
       <c r="D51" s="3" t="s">
         <v>99</v>
       </c>
@@ -6849,9 +6833,9 @@
       <c r="L51" s="3"/>
       <c r="M51" s="3"/>
     </row>
-    <row r="52" spans="2:13">
-      <c r="B52" s="173"/>
-      <c r="C52" s="173"/>
+    <row r="52" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B52" s="169"/>
+      <c r="C52" s="169"/>
       <c r="D52" s="3" t="s">
         <v>102</v>
       </c>
@@ -6869,9 +6853,9 @@
       <c r="L52" s="3"/>
       <c r="M52" s="3"/>
     </row>
-    <row r="53" spans="2:13">
-      <c r="B53" s="173"/>
-      <c r="C53" s="173"/>
+    <row r="53" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B53" s="169"/>
+      <c r="C53" s="169"/>
       <c r="D53" s="3" t="s">
         <v>105</v>
       </c>
@@ -6889,9 +6873,9 @@
       <c r="L53" s="3"/>
       <c r="M53" s="3"/>
     </row>
-    <row r="54" spans="2:13" ht="29.1">
-      <c r="B54" s="173"/>
-      <c r="C54" s="173"/>
+    <row r="54" spans="2:13" ht="29" x14ac:dyDescent="0.35">
+      <c r="B54" s="169"/>
+      <c r="C54" s="169"/>
       <c r="D54" s="2" t="s">
         <v>108</v>
       </c>
@@ -6909,9 +6893,9 @@
       <c r="L54" s="3"/>
       <c r="M54" s="3"/>
     </row>
-    <row r="55" spans="2:13">
-      <c r="B55" s="173"/>
-      <c r="C55" s="173"/>
+    <row r="55" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B55" s="169"/>
+      <c r="C55" s="169"/>
       <c r="D55" s="2" t="s">
         <v>111</v>
       </c>
@@ -6929,9 +6913,9 @@
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
     </row>
-    <row r="56" spans="2:13">
-      <c r="B56" s="173"/>
-      <c r="C56" s="173"/>
+    <row r="56" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B56" s="169"/>
+      <c r="C56" s="169"/>
       <c r="D56" s="2" t="s">
         <v>44</v>
       </c>
@@ -6949,9 +6933,9 @@
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
     </row>
-    <row r="57" spans="2:13">
-      <c r="B57" s="173"/>
-      <c r="C57" s="173"/>
+    <row r="57" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B57" s="169"/>
+      <c r="C57" s="169"/>
       <c r="D57" s="3" t="s">
         <v>114</v>
       </c>
@@ -6969,9 +6953,9 @@
       <c r="L57" s="3"/>
       <c r="M57" s="3"/>
     </row>
-    <row r="58" spans="2:13">
-      <c r="B58" s="173"/>
-      <c r="C58" s="173"/>
+    <row r="58" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B58" s="169"/>
+      <c r="C58" s="169"/>
       <c r="D58" s="3" t="s">
         <v>116</v>
       </c>
@@ -6985,9 +6969,9 @@
       <c r="L58" s="3"/>
       <c r="M58" s="3"/>
     </row>
-    <row r="59" spans="2:13">
-      <c r="B59" s="173"/>
-      <c r="C59" s="173"/>
+    <row r="59" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B59" s="169"/>
+      <c r="C59" s="169"/>
       <c r="D59" s="3" t="s">
         <v>117</v>
       </c>
@@ -7001,9 +6985,9 @@
       <c r="L59" s="3"/>
       <c r="M59" s="3"/>
     </row>
-    <row r="60" spans="2:13">
-      <c r="B60" s="173"/>
-      <c r="C60" s="173"/>
+    <row r="60" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B60" s="169"/>
+      <c r="C60" s="169"/>
       <c r="D60" s="3" t="s">
         <v>38</v>
       </c>
@@ -7021,9 +7005,9 @@
       <c r="L60" s="3"/>
       <c r="M60" s="3"/>
     </row>
-    <row r="61" spans="2:13">
-      <c r="B61" s="173"/>
-      <c r="C61" s="173"/>
+    <row r="61" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B61" s="169"/>
+      <c r="C61" s="169"/>
       <c r="D61" s="45" t="s">
         <v>120</v>
       </c>
@@ -7037,11 +7021,11 @@
       <c r="L61" s="3"/>
       <c r="M61" s="3"/>
     </row>
-    <row r="62" spans="2:13">
-      <c r="B62" s="173">
+    <row r="62" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B62" s="169">
         <v>7</v>
       </c>
-      <c r="C62" s="173" t="s">
+      <c r="C62" s="169" t="s">
         <v>121</v>
       </c>
       <c r="D62" s="43" t="s">
@@ -7061,9 +7045,9 @@
       <c r="L62" s="3"/>
       <c r="M62" s="3"/>
     </row>
-    <row r="63" spans="2:13">
-      <c r="B63" s="173"/>
-      <c r="C63" s="173"/>
+    <row r="63" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B63" s="169"/>
+      <c r="C63" s="169"/>
       <c r="D63" s="3" t="s">
         <v>125</v>
       </c>
@@ -7081,9 +7065,9 @@
       <c r="L63" s="3"/>
       <c r="M63" s="3"/>
     </row>
-    <row r="64" spans="2:13">
-      <c r="B64" s="173"/>
-      <c r="C64" s="173"/>
+    <row r="64" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B64" s="169"/>
+      <c r="C64" s="169"/>
       <c r="D64" s="3" t="s">
         <v>71</v>
       </c>
@@ -7097,9 +7081,9 @@
       <c r="L64" s="3"/>
       <c r="M64" s="3"/>
     </row>
-    <row r="65" spans="2:13">
-      <c r="B65" s="173"/>
-      <c r="C65" s="173"/>
+    <row r="65" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B65" s="169"/>
+      <c r="C65" s="169"/>
       <c r="D65" s="3" t="s">
         <v>127</v>
       </c>
@@ -7117,9 +7101,9 @@
       <c r="L65" s="3"/>
       <c r="M65" s="3"/>
     </row>
-    <row r="66" spans="2:13">
-      <c r="B66" s="173"/>
-      <c r="C66" s="173"/>
+    <row r="66" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B66" s="169"/>
+      <c r="C66" s="169"/>
       <c r="D66" s="3" t="s">
         <v>129</v>
       </c>
@@ -7137,9 +7121,9 @@
       <c r="L66" s="3"/>
       <c r="M66" s="3"/>
     </row>
-    <row r="67" spans="2:13">
-      <c r="B67" s="173"/>
-      <c r="C67" s="173"/>
+    <row r="67" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B67" s="169"/>
+      <c r="C67" s="169"/>
       <c r="D67" s="3" t="s">
         <v>131</v>
       </c>
@@ -7159,12 +7143,11 @@
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="B32:B49"/>
-    <mergeCell ref="C32:C49"/>
-    <mergeCell ref="B50:B61"/>
-    <mergeCell ref="C50:C61"/>
-    <mergeCell ref="B62:B67"/>
-    <mergeCell ref="C62:C67"/>
+    <mergeCell ref="B26:B31"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="E2:E3"/>
     <mergeCell ref="H2:H3"/>
     <mergeCell ref="J2:M2"/>
     <mergeCell ref="B4:B11"/>
@@ -7172,11 +7155,12 @@
     <mergeCell ref="B24:B25"/>
     <mergeCell ref="F2:F3"/>
     <mergeCell ref="G2:G3"/>
-    <mergeCell ref="B26:B31"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="B32:B49"/>
+    <mergeCell ref="C32:C49"/>
+    <mergeCell ref="B50:B61"/>
+    <mergeCell ref="C50:C61"/>
+    <mergeCell ref="B62:B67"/>
+    <mergeCell ref="C62:C67"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -7188,74 +7172,74 @@
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
   <dimension ref="A1:I23"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="35"/>
-    <col min="2" max="2" width="19.42578125" style="35" customWidth="1"/>
-    <col min="3" max="3" width="55.140625" style="35" customWidth="1"/>
-    <col min="4" max="4" width="29.42578125" style="35" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="25.85546875" style="35" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="41.140625" style="35" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="35.5703125" style="69" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.85546875" style="70" customWidth="1"/>
+    <col min="1" max="1" width="9.1796875" style="35"/>
+    <col min="2" max="2" width="19.453125" style="35" customWidth="1"/>
+    <col min="3" max="3" width="55.1796875" style="35" customWidth="1"/>
+    <col min="4" max="4" width="29.453125" style="35" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="25.81640625" style="35" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="41.1796875" style="35" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="35.54296875" style="69" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.81640625" style="70" customWidth="1"/>
     <col min="9" max="9" width="23" style="35" customWidth="1"/>
-    <col min="10" max="16384" width="9.140625" style="35"/>
+    <col min="10" max="16384" width="9.1796875" style="35"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="23.45">
+    <row r="1" spans="1:9" ht="23.5" x14ac:dyDescent="0.35">
       <c r="B1" s="37" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="26.1" customHeight="1">
-      <c r="B2" s="195" t="s">
+    <row r="2" spans="1:9" ht="26.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B2" s="193" t="s">
         <v>497</v>
       </c>
-      <c r="C2" s="196"/>
-      <c r="D2" s="172"/>
-      <c r="E2" s="172"/>
-      <c r="F2" s="172"/>
-    </row>
-    <row r="3" spans="1:9" ht="26.1" customHeight="1">
+      <c r="C2" s="194"/>
+      <c r="D2" s="173"/>
+      <c r="E2" s="173"/>
+      <c r="F2" s="173"/>
+    </row>
+    <row r="3" spans="1:9" ht="26.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B3" s="51"/>
       <c r="C3" s="52"/>
       <c r="D3" s="138"/>
       <c r="E3" s="139"/>
       <c r="F3" s="139"/>
     </row>
-    <row r="4" spans="1:9" ht="26.1" customHeight="1">
+    <row r="4" spans="1:9" ht="26.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B4" s="140"/>
       <c r="C4" s="141"/>
       <c r="D4" s="142"/>
       <c r="E4" s="143"/>
       <c r="F4" s="143"/>
     </row>
-    <row r="5" spans="1:9" ht="26.1" customHeight="1">
-      <c r="A5" s="183" t="s">
+    <row r="5" spans="1:9" ht="26.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="181" t="s">
         <v>498</v>
       </c>
-      <c r="B5" s="183"/>
-      <c r="C5" s="183"/>
-      <c r="D5" s="183"/>
-      <c r="E5" s="183"/>
-      <c r="F5" s="183"/>
-      <c r="G5" s="183"/>
-      <c r="H5" s="183"/>
-    </row>
-    <row r="6" spans="1:9" ht="32.450000000000003" customHeight="1">
-      <c r="A6" s="197" t="s">
+      <c r="B5" s="181"/>
+      <c r="C5" s="181"/>
+      <c r="D5" s="181"/>
+      <c r="E5" s="181"/>
+      <c r="F5" s="181"/>
+      <c r="G5" s="181"/>
+      <c r="H5" s="181"/>
+    </row>
+    <row r="6" spans="1:9" ht="32.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="195" t="s">
         <v>499</v>
       </c>
-      <c r="B6" s="197"/>
-      <c r="C6" s="197"/>
-      <c r="D6" s="197"/>
-      <c r="E6" s="197"/>
-      <c r="F6" s="197"/>
-      <c r="G6" s="197"/>
-      <c r="H6" s="197"/>
+      <c r="B6" s="195"/>
+      <c r="C6" s="195"/>
+      <c r="D6" s="195"/>
+      <c r="E6" s="195"/>
+      <c r="F6" s="195"/>
+      <c r="G6" s="195"/>
+      <c r="H6" s="195"/>
       <c r="I6"/>
     </row>
-    <row r="7" spans="1:9" ht="30.95">
+    <row r="7" spans="1:9" ht="31" x14ac:dyDescent="0.35">
       <c r="A7" s="28" t="s">
         <v>293</v>
       </c>
@@ -7284,7 +7268,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="29.1">
+    <row r="8" spans="1:9" ht="29" x14ac:dyDescent="0.35">
       <c r="A8" s="6" t="s">
         <v>501</v>
       </c>
@@ -7311,7 +7295,7 @@
       </c>
       <c r="I8" s="6"/>
     </row>
-    <row r="9" spans="1:9" ht="43.5">
+    <row r="9" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A9" s="6" t="s">
         <v>504</v>
       </c>
@@ -7338,7 +7322,7 @@
       </c>
       <c r="I9" s="6"/>
     </row>
-    <row r="10" spans="1:9" ht="43.5">
+    <row r="10" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A10" s="6" t="s">
         <v>507</v>
       </c>
@@ -7365,7 +7349,7 @@
       </c>
       <c r="I10" s="6"/>
     </row>
-    <row r="11" spans="1:9" ht="43.5">
+    <row r="11" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A11" s="6" t="s">
         <v>510</v>
       </c>
@@ -7390,7 +7374,7 @@
       </c>
       <c r="I11" s="6"/>
     </row>
-    <row r="12" spans="1:9" ht="43.5">
+    <row r="12" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A12" s="6" t="s">
         <v>513</v>
       </c>
@@ -7415,7 +7399,7 @@
       </c>
       <c r="I12" s="63"/>
     </row>
-    <row r="13" spans="1:9">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A13" s="6" t="s">
         <v>517</v>
       </c>
@@ -7440,7 +7424,7 @@
       </c>
       <c r="I13" s="6"/>
     </row>
-    <row r="14" spans="1:9" ht="144.94999999999999">
+    <row r="14" spans="1:9" ht="145" x14ac:dyDescent="0.35">
       <c r="A14" s="6" t="s">
         <v>522</v>
       </c>
@@ -7465,7 +7449,7 @@
       </c>
       <c r="I14" s="6"/>
     </row>
-    <row r="15" spans="1:9">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A15" s="6" t="s">
         <v>524</v>
       </c>
@@ -7490,7 +7474,7 @@
       </c>
       <c r="I15" s="6"/>
     </row>
-    <row r="16" spans="1:9" ht="43.5">
+    <row r="16" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A16" s="6" t="s">
         <v>526</v>
       </c>
@@ -7515,7 +7499,7 @@
       </c>
       <c r="I16" s="6"/>
     </row>
-    <row r="17" spans="1:9" ht="29.1">
+    <row r="17" spans="1:9" ht="29" x14ac:dyDescent="0.35">
       <c r="A17" s="6" t="s">
         <v>530</v>
       </c>
@@ -7540,7 +7524,7 @@
       </c>
       <c r="I17" s="6"/>
     </row>
-    <row r="18" spans="1:9" ht="29.1">
+    <row r="18" spans="1:9" ht="29" x14ac:dyDescent="0.35">
       <c r="A18" s="6" t="s">
         <v>534</v>
       </c>
@@ -7565,7 +7549,7 @@
       </c>
       <c r="I18" s="6"/>
     </row>
-    <row r="19" spans="1:9" ht="43.5">
+    <row r="19" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A19" s="6" t="s">
         <v>538</v>
       </c>
@@ -7590,7 +7574,7 @@
       </c>
       <c r="I19" s="6"/>
     </row>
-    <row r="20" spans="1:9" ht="41.45" customHeight="1">
+    <row r="20" spans="1:9" ht="41.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="6" t="s">
         <v>541</v>
       </c>
@@ -7615,7 +7599,7 @@
       </c>
       <c r="I20" s="6"/>
     </row>
-    <row r="21" spans="1:9" ht="43.5">
+    <row r="21" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A21" s="6" t="s">
         <v>545</v>
       </c>
@@ -7640,10 +7624,10 @@
       </c>
       <c r="I21" s="6"/>
     </row>
-    <row r="22" spans="1:9">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="F22" s="61"/>
     </row>
-    <row r="23" spans="1:9">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B23" s="35" t="s">
         <v>548</v>
       </c>
@@ -7655,7 +7639,7 @@
       <selection activeCell="H4" sqref="H4:J11"/>
       <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
       <pageSetup orientation="portrait" r:id="rId1"/>
-      <autoFilter ref="A2:O16" xr:uid="{37C00C12-4487-4227-9A21-A4C397DBB433}">
+      <autoFilter ref="A2:O16" xr:uid="{A32CD63E-D77B-49C0-A296-A4378B8086AC}">
         <filterColumn colId="11">
           <filters>
             <filter val="No"/>
@@ -7691,73 +7675,73 @@
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
   <dimension ref="A1:I14"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="26.140625" customWidth="1"/>
-    <col min="3" max="3" width="31.140625" customWidth="1"/>
-    <col min="4" max="4" width="21.140625" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="24.140625" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="21.140625" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="35.28515625" style="114" customWidth="1"/>
-    <col min="8" max="8" width="20.42578125" style="114" customWidth="1"/>
-    <col min="9" max="9" width="28.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.1796875" customWidth="1"/>
+    <col min="3" max="3" width="31.1796875" customWidth="1"/>
+    <col min="4" max="4" width="21.1796875" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="24.1796875" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="21.1796875" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="35.26953125" style="114" customWidth="1"/>
+    <col min="8" max="8" width="20.453125" style="114" customWidth="1"/>
+    <col min="9" max="9" width="28.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="23.45" customHeight="1">
+    <row r="1" spans="1:9" ht="23.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B1" s="30" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="39.6" customHeight="1">
-      <c r="B2" s="198" t="s">
+    <row r="2" spans="1:9" ht="39.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B2" s="196" t="s">
         <v>549</v>
       </c>
-      <c r="C2" s="199"/>
-      <c r="D2" s="171"/>
-      <c r="E2" s="171"/>
-      <c r="F2" s="171"/>
-    </row>
-    <row r="3" spans="1:9" ht="39.6" customHeight="1">
+      <c r="C2" s="197"/>
+      <c r="D2" s="172"/>
+      <c r="E2" s="172"/>
+      <c r="F2" s="172"/>
+    </row>
+    <row r="3" spans="1:9" ht="39.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B3" s="49"/>
       <c r="C3" s="49"/>
       <c r="D3" s="62"/>
       <c r="E3" s="62"/>
       <c r="F3" s="62"/>
     </row>
-    <row r="4" spans="1:9" ht="39.6" customHeight="1">
+    <row r="4" spans="1:9" ht="39.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B4" s="126"/>
       <c r="C4" s="126"/>
       <c r="D4" s="62"/>
       <c r="E4" s="62"/>
       <c r="F4" s="62"/>
     </row>
-    <row r="5" spans="1:9" ht="39.6" customHeight="1">
-      <c r="A5" s="200" t="s">
+    <row r="5" spans="1:9" ht="39.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="198" t="s">
         <v>550</v>
       </c>
-      <c r="B5" s="201"/>
-      <c r="C5" s="201"/>
-      <c r="D5" s="201"/>
-      <c r="E5" s="201"/>
-      <c r="F5" s="201"/>
-      <c r="G5" s="201"/>
-      <c r="H5" s="202"/>
+      <c r="B5" s="199"/>
+      <c r="C5" s="199"/>
+      <c r="D5" s="199"/>
+      <c r="E5" s="199"/>
+      <c r="F5" s="199"/>
+      <c r="G5" s="199"/>
+      <c r="H5" s="200"/>
       <c r="I5" s="87"/>
     </row>
-    <row r="6" spans="1:9" ht="39.6" customHeight="1">
-      <c r="A6" s="203" t="s">
+    <row r="6" spans="1:9" ht="39.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="201" t="s">
         <v>551</v>
       </c>
-      <c r="B6" s="204"/>
-      <c r="C6" s="204"/>
-      <c r="D6" s="204"/>
-      <c r="E6" s="204"/>
-      <c r="F6" s="204"/>
-      <c r="G6" s="204"/>
-      <c r="H6" s="205"/>
+      <c r="B6" s="202"/>
+      <c r="C6" s="202"/>
+      <c r="D6" s="202"/>
+      <c r="E6" s="202"/>
+      <c r="F6" s="202"/>
+      <c r="G6" s="202"/>
+      <c r="H6" s="203"/>
       <c r="I6" s="8"/>
     </row>
-    <row r="7" spans="1:9" ht="41.1" customHeight="1">
+    <row r="7" spans="1:9" ht="41.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="28" t="s">
         <v>293</v>
       </c>
@@ -7786,7 +7770,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="43.5">
+    <row r="8" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A8" s="6" t="s">
         <v>552</v>
       </c>
@@ -7813,7 +7797,7 @@
       </c>
       <c r="I8" s="6"/>
     </row>
-    <row r="9" spans="1:9" ht="29.1">
+    <row r="9" spans="1:9" ht="29" x14ac:dyDescent="0.35">
       <c r="A9" s="6" t="s">
         <v>557</v>
       </c>
@@ -7840,7 +7824,7 @@
       </c>
       <c r="I9" s="6"/>
     </row>
-    <row r="10" spans="1:9" ht="43.5">
+    <row r="10" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A10" s="6" t="s">
         <v>559</v>
       </c>
@@ -7867,7 +7851,7 @@
       </c>
       <c r="I10" s="6"/>
     </row>
-    <row r="11" spans="1:9" ht="43.5">
+    <row r="11" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A11" s="6" t="s">
         <v>563</v>
       </c>
@@ -7894,7 +7878,7 @@
       </c>
       <c r="I11" s="6"/>
     </row>
-    <row r="14" spans="1:9">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B14" t="s">
         <v>568</v>
       </c>
@@ -7928,71 +7912,71 @@
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
   <dimension ref="A1:I11"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="26.140625" customWidth="1"/>
-    <col min="3" max="3" width="31.140625" customWidth="1"/>
-    <col min="4" max="4" width="21.140625" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="24.140625" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="21.140625" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="31.140625" customWidth="1"/>
-    <col min="8" max="8" width="16.85546875" customWidth="1"/>
+    <col min="1" max="1" width="10.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.1796875" customWidth="1"/>
+    <col min="3" max="3" width="31.1796875" customWidth="1"/>
+    <col min="4" max="4" width="21.1796875" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="24.1796875" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="21.1796875" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="31.1796875" customWidth="1"/>
+    <col min="8" max="8" width="16.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="23.45" customHeight="1">
+    <row r="1" spans="1:9" ht="23.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B1" s="30" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="39.6" customHeight="1">
-      <c r="B2" s="198" t="s">
+    <row r="2" spans="1:9" ht="39.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B2" s="196" t="s">
         <v>549</v>
       </c>
-      <c r="C2" s="199"/>
-      <c r="D2" s="171"/>
-      <c r="E2" s="171"/>
-      <c r="F2" s="171"/>
-    </row>
-    <row r="3" spans="1:9" ht="39.6" customHeight="1">
+      <c r="C2" s="197"/>
+      <c r="D2" s="172"/>
+      <c r="E2" s="172"/>
+      <c r="F2" s="172"/>
+    </row>
+    <row r="3" spans="1:9" ht="39.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B3" s="49"/>
       <c r="C3" s="49"/>
       <c r="D3" s="62"/>
       <c r="E3" s="62"/>
       <c r="F3" s="62"/>
     </row>
-    <row r="4" spans="1:9" ht="39.6" customHeight="1">
+    <row r="4" spans="1:9" ht="39.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B4" s="126"/>
       <c r="C4" s="126"/>
       <c r="D4" s="62"/>
       <c r="E4" s="62"/>
       <c r="F4" s="62"/>
     </row>
-    <row r="5" spans="1:9" ht="39.6" customHeight="1">
-      <c r="A5" s="200" t="s">
+    <row r="5" spans="1:9" ht="39.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="198" t="s">
         <v>569</v>
       </c>
-      <c r="B5" s="201"/>
-      <c r="C5" s="201"/>
-      <c r="D5" s="201"/>
-      <c r="E5" s="201"/>
-      <c r="F5" s="201"/>
-      <c r="G5" s="201"/>
-      <c r="H5" s="202"/>
-    </row>
-    <row r="6" spans="1:9" ht="39.6" customHeight="1">
-      <c r="A6" s="188" t="s">
+      <c r="B5" s="199"/>
+      <c r="C5" s="199"/>
+      <c r="D5" s="199"/>
+      <c r="E5" s="199"/>
+      <c r="F5" s="199"/>
+      <c r="G5" s="199"/>
+      <c r="H5" s="200"/>
+    </row>
+    <row r="6" spans="1:9" ht="39.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="186" t="s">
         <v>570</v>
       </c>
-      <c r="B6" s="188"/>
-      <c r="C6" s="188"/>
-      <c r="D6" s="188"/>
-      <c r="E6" s="188"/>
-      <c r="F6" s="188"/>
-      <c r="G6" s="188"/>
-      <c r="H6" s="188"/>
-    </row>
-    <row r="7" spans="1:9" ht="41.1" customHeight="1">
+      <c r="B6" s="186"/>
+      <c r="C6" s="186"/>
+      <c r="D6" s="186"/>
+      <c r="E6" s="186"/>
+      <c r="F6" s="186"/>
+      <c r="G6" s="186"/>
+      <c r="H6" s="186"/>
+    </row>
+    <row r="7" spans="1:9" ht="41.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="28" t="s">
         <v>293</v>
       </c>
@@ -8021,7 +8005,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="43.5">
+    <row r="8" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A8" s="6" t="s">
         <v>571</v>
       </c>
@@ -8048,7 +8032,7 @@
       </c>
       <c r="I8" s="20"/>
     </row>
-    <row r="9" spans="1:9" ht="43.5">
+    <row r="9" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A9" s="6" t="s">
         <v>572</v>
       </c>
@@ -8075,7 +8059,7 @@
       </c>
       <c r="I9" s="20"/>
     </row>
-    <row r="10" spans="1:9" ht="43.5">
+    <row r="10" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A10" s="6" t="s">
         <v>573</v>
       </c>
@@ -8102,7 +8086,7 @@
       </c>
       <c r="I10" s="20"/>
     </row>
-    <row r="11" spans="1:9" ht="43.5">
+    <row r="11" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A11" s="6" t="s">
         <v>575</v>
       </c>
@@ -8157,67 +8141,67 @@
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
   <dimension ref="A1:H38"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="34.85546875" customWidth="1"/>
-    <col min="3" max="3" width="35.42578125" customWidth="1"/>
-    <col min="4" max="4" width="34.42578125" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="34.81640625" customWidth="1"/>
+    <col min="3" max="3" width="35.453125" customWidth="1"/>
+    <col min="4" max="4" width="34.453125" hidden="1" customWidth="1"/>
     <col min="5" max="5" width="25" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="37.42578125" customWidth="1"/>
-    <col min="7" max="7" width="17.5703125" customWidth="1"/>
-    <col min="8" max="8" width="32.140625" customWidth="1"/>
+    <col min="6" max="6" width="37.453125" customWidth="1"/>
+    <col min="7" max="7" width="17.54296875" customWidth="1"/>
+    <col min="8" max="8" width="32.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="23.45">
+    <row r="1" spans="1:8" ht="23.5" x14ac:dyDescent="0.55000000000000004">
       <c r="B1" s="30" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="34.5" customHeight="1">
-      <c r="B2" s="169" t="s">
+    <row r="2" spans="1:8" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B2" s="204" t="s">
         <v>576</v>
       </c>
-      <c r="C2" s="170"/>
-      <c r="D2" s="171"/>
-      <c r="E2" s="171"/>
-    </row>
-    <row r="3" spans="1:8" ht="34.5" customHeight="1">
+      <c r="C2" s="205"/>
+      <c r="D2" s="172"/>
+      <c r="E2" s="172"/>
+    </row>
+    <row r="3" spans="1:8" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B3" s="150"/>
       <c r="C3" s="151"/>
       <c r="D3" s="62"/>
       <c r="E3" s="62"/>
     </row>
-    <row r="4" spans="1:8" ht="34.5" customHeight="1">
+    <row r="4" spans="1:8" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B4" s="150"/>
       <c r="C4" s="151"/>
       <c r="D4" s="62"/>
       <c r="E4" s="62"/>
     </row>
-    <row r="5" spans="1:8" ht="34.5" customHeight="1">
-      <c r="A5" s="172" t="s">
+    <row r="5" spans="1:8" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="173" t="s">
         <v>577</v>
       </c>
-      <c r="B5" s="172"/>
-      <c r="C5" s="172"/>
-      <c r="D5" s="172"/>
-      <c r="E5" s="172"/>
-      <c r="F5" s="172"/>
-      <c r="G5" s="172"/>
+      <c r="B5" s="173"/>
+      <c r="C5" s="173"/>
+      <c r="D5" s="173"/>
+      <c r="E5" s="173"/>
+      <c r="F5" s="173"/>
+      <c r="G5" s="173"/>
       <c r="H5" s="155"/>
     </row>
-    <row r="6" spans="1:8" ht="29.1" customHeight="1">
-      <c r="A6" s="173" t="s">
+    <row r="6" spans="1:8" ht="29.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="169" t="s">
         <v>578</v>
       </c>
-      <c r="B6" s="173"/>
-      <c r="C6" s="173"/>
-      <c r="D6" s="173"/>
-      <c r="E6" s="173"/>
-      <c r="F6" s="173"/>
-      <c r="G6" s="173"/>
+      <c r="B6" s="169"/>
+      <c r="C6" s="169"/>
+      <c r="D6" s="169"/>
+      <c r="E6" s="169"/>
+      <c r="F6" s="169"/>
+      <c r="G6" s="169"/>
       <c r="H6" s="20"/>
     </row>
-    <row r="7" spans="1:8" s="35" customFormat="1" ht="54.75" customHeight="1">
+    <row r="7" spans="1:8" s="35" customFormat="1" ht="54.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="28" t="s">
         <v>293</v>
       </c>
@@ -8243,7 +8227,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="43.5">
+    <row r="8" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A8" s="6" t="s">
         <v>579</v>
       </c>
@@ -8269,7 +8253,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="43.5">
+    <row r="9" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A9" s="6" t="s">
         <v>583</v>
       </c>
@@ -8293,7 +8277,7 @@
       </c>
       <c r="H9" s="6"/>
     </row>
-    <row r="10" spans="1:8" ht="43.5">
+    <row r="10" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A10" s="6" t="s">
         <v>586</v>
       </c>
@@ -8315,7 +8299,7 @@
       </c>
       <c r="H10" s="6"/>
     </row>
-    <row r="11" spans="1:8" ht="43.5">
+    <row r="11" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A11" s="6" t="s">
         <v>589</v>
       </c>
@@ -8337,7 +8321,7 @@
       </c>
       <c r="H11" s="6"/>
     </row>
-    <row r="12" spans="1:8" ht="43.5">
+    <row r="12" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A12" s="6" t="s">
         <v>592</v>
       </c>
@@ -8361,7 +8345,7 @@
       </c>
       <c r="H12" s="6"/>
     </row>
-    <row r="13" spans="1:8" ht="43.5">
+    <row r="13" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A13" s="6" t="s">
         <v>595</v>
       </c>
@@ -8385,7 +8369,7 @@
       </c>
       <c r="H13" s="6"/>
     </row>
-    <row r="14" spans="1:8" ht="43.5">
+    <row r="14" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A14" s="6" t="s">
         <v>599</v>
       </c>
@@ -8409,7 +8393,7 @@
       </c>
       <c r="H14" s="6"/>
     </row>
-    <row r="15" spans="1:8" ht="43.5">
+    <row r="15" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A15" s="6" t="s">
         <v>603</v>
       </c>
@@ -8433,7 +8417,7 @@
       </c>
       <c r="H15" s="6"/>
     </row>
-    <row r="16" spans="1:8" ht="43.5">
+    <row r="16" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A16" s="6" t="s">
         <v>606</v>
       </c>
@@ -8457,7 +8441,7 @@
       </c>
       <c r="H16" s="6"/>
     </row>
-    <row r="17" spans="1:8" ht="43.5">
+    <row r="17" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A17" s="6" t="s">
         <v>609</v>
       </c>
@@ -8481,7 +8465,7 @@
       </c>
       <c r="H17" s="6"/>
     </row>
-    <row r="18" spans="1:8" ht="43.5">
+    <row r="18" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A18" s="6" t="s">
         <v>612</v>
       </c>
@@ -8503,7 +8487,7 @@
       </c>
       <c r="H18" s="6"/>
     </row>
-    <row r="19" spans="1:8" ht="43.5">
+    <row r="19" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A19" s="6" t="s">
         <v>614</v>
       </c>
@@ -8525,7 +8509,7 @@
       </c>
       <c r="H19" s="6"/>
     </row>
-    <row r="20" spans="1:8" ht="43.5">
+    <row r="20" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A20" s="6" t="s">
         <v>616</v>
       </c>
@@ -8549,7 +8533,7 @@
       </c>
       <c r="H20" s="6"/>
     </row>
-    <row r="21" spans="1:8" ht="43.5">
+    <row r="21" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A21" s="6" t="s">
         <v>619</v>
       </c>
@@ -8573,7 +8557,7 @@
       </c>
       <c r="H21" s="6"/>
     </row>
-    <row r="22" spans="1:8" ht="43.5">
+    <row r="22" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A22" s="6" t="s">
         <v>622</v>
       </c>
@@ -8597,7 +8581,7 @@
       </c>
       <c r="H22" s="6"/>
     </row>
-    <row r="23" spans="1:8" ht="43.5">
+    <row r="23" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A23" s="6" t="s">
         <v>625</v>
       </c>
@@ -8621,7 +8605,7 @@
       </c>
       <c r="H23" s="6"/>
     </row>
-    <row r="24" spans="1:8" ht="43.5">
+    <row r="24" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A24" s="6" t="s">
         <v>628</v>
       </c>
@@ -8645,7 +8629,7 @@
       </c>
       <c r="H24" s="6"/>
     </row>
-    <row r="25" spans="1:8" ht="43.5">
+    <row r="25" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A25" s="6" t="s">
         <v>632</v>
       </c>
@@ -8669,7 +8653,7 @@
       </c>
       <c r="H25" s="6"/>
     </row>
-    <row r="26" spans="1:8" ht="43.5">
+    <row r="26" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A26" s="6" t="s">
         <v>635</v>
       </c>
@@ -8693,7 +8677,7 @@
       </c>
       <c r="H26" s="6"/>
     </row>
-    <row r="27" spans="1:8" ht="43.5">
+    <row r="27" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A27" s="6" t="s">
         <v>638</v>
       </c>
@@ -8717,7 +8701,7 @@
       </c>
       <c r="H27" s="6"/>
     </row>
-    <row r="28" spans="1:8" ht="43.5">
+    <row r="28" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A28" s="6" t="s">
         <v>641</v>
       </c>
@@ -8741,7 +8725,7 @@
       </c>
       <c r="H28" s="158"/>
     </row>
-    <row r="29" spans="1:8" s="35" customFormat="1" ht="30.75">
+    <row r="29" spans="1:8" s="35" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A29" s="6" t="s">
         <v>645</v>
       </c>
@@ -8761,7 +8745,7 @@
       </c>
       <c r="H29" s="158"/>
     </row>
-    <row r="30" spans="1:8" ht="43.5">
+    <row r="30" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A30" s="6" t="s">
         <v>648</v>
       </c>
@@ -8783,7 +8767,7 @@
       </c>
       <c r="H30" s="66"/>
     </row>
-    <row r="31" spans="1:8" ht="30.75">
+    <row r="31" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A31" s="6" t="s">
         <v>650</v>
       </c>
@@ -8801,7 +8785,7 @@
       </c>
       <c r="H31" s="161"/>
     </row>
-    <row r="32" spans="1:8" ht="15">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A32" s="6" t="s">
         <v>653</v>
       </c>
@@ -8819,19 +8803,19 @@
       </c>
       <c r="H32" s="161"/>
     </row>
-    <row r="34" spans="2:2">
+    <row r="34" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B34" s="11"/>
     </row>
-    <row r="35" spans="2:2">
+    <row r="35" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B35" s="11"/>
     </row>
-    <row r="36" spans="2:2">
+    <row r="36" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B36" s="11"/>
     </row>
-    <row r="37" spans="2:2">
+    <row r="37" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B37" s="11"/>
     </row>
-    <row r="38" spans="2:2">
+    <row r="38" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B38" s="11"/>
     </row>
   </sheetData>
@@ -8869,37 +8853,37 @@
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
   <dimension ref="A1:G7"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="19.5703125" customWidth="1"/>
-    <col min="2" max="2" width="27.42578125" customWidth="1"/>
-    <col min="3" max="3" width="13.85546875" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="19.54296875" customWidth="1"/>
+    <col min="2" max="2" width="27.453125" customWidth="1"/>
+    <col min="3" max="3" width="13.81640625" hidden="1" customWidth="1"/>
     <col min="4" max="5" width="0" hidden="1" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="21">
+    <row r="1" spans="1:7" ht="21" x14ac:dyDescent="0.5">
       <c r="A1" s="29" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="45.6" customHeight="1">
+    <row r="2" spans="1:7" ht="45.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="206" t="s">
         <v>654</v>
       </c>
       <c r="B2" s="206"/>
-      <c r="C2" s="171"/>
-      <c r="D2" s="171"/>
-      <c r="E2" s="171"/>
-    </row>
-    <row r="3" spans="1:7" ht="45.6" customHeight="1">
+      <c r="C2" s="172"/>
+      <c r="D2" s="172"/>
+      <c r="E2" s="172"/>
+    </row>
+    <row r="3" spans="1:7" ht="45.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="27"/>
       <c r="B3" s="27"/>
       <c r="C3" s="54"/>
       <c r="D3" s="54"/>
       <c r="E3" s="54"/>
     </row>
-    <row r="4" spans="1:7" ht="44.25" customHeight="1">
+    <row r="4" spans="1:7" ht="44.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="31" t="s">
         <v>230</v>
       </c>
@@ -8922,7 +8906,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" s="20" t="s">
         <v>342</v>
       </c>
@@ -8935,7 +8919,7 @@
       </c>
       <c r="G5" s="25"/>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" s="20" t="s">
         <v>240</v>
       </c>
@@ -8948,7 +8932,7 @@
       </c>
       <c r="G6" s="3"/>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" s="21" t="s">
         <v>657</v>
       </c>
@@ -8986,37 +8970,37 @@
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
   <dimension ref="A1:G7"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.85546875" customWidth="1"/>
-    <col min="3" max="3" width="8.7109375" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="15.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.81640625" customWidth="1"/>
+    <col min="3" max="3" width="8.7265625" hidden="1" customWidth="1"/>
     <col min="4" max="5" width="0" hidden="1" customWidth="1"/>
     <col min="6" max="6" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="23.45">
+    <row r="1" spans="1:7" ht="23.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="30" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="46.35" customHeight="1">
-      <c r="A2" s="184" t="s">
+    <row r="2" spans="1:7" ht="46.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="182" t="s">
         <v>658</v>
       </c>
-      <c r="B2" s="184"/>
-      <c r="C2" s="171"/>
-      <c r="D2" s="171"/>
-      <c r="E2" s="171"/>
-    </row>
-    <row r="3" spans="1:7" ht="46.35" customHeight="1">
+      <c r="B2" s="182"/>
+      <c r="C2" s="172"/>
+      <c r="D2" s="172"/>
+      <c r="E2" s="172"/>
+    </row>
+    <row r="3" spans="1:7" ht="46.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="49"/>
       <c r="B3" s="49"/>
       <c r="C3" s="54"/>
       <c r="D3" s="54"/>
       <c r="E3" s="54"/>
     </row>
-    <row r="4" spans="1:7" ht="62.1">
+    <row r="4" spans="1:7" ht="62" x14ac:dyDescent="0.35">
       <c r="A4" s="38" t="s">
         <v>230</v>
       </c>
@@ -9039,7 +9023,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" s="44" t="s">
         <v>659</v>
       </c>
@@ -9052,7 +9036,7 @@
       </c>
       <c r="G5" s="25"/>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" s="20" t="s">
         <v>342</v>
       </c>
@@ -9065,7 +9049,7 @@
       </c>
       <c r="G6" s="3"/>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" s="21" t="s">
         <v>660</v>
       </c>
@@ -9100,34 +9084,34 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D69FD0C8-106C-4C83-AF06-346874FADF60}">
   <dimension ref="B1:AH101"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.81640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="39" customWidth="1"/>
-    <col min="5" max="5" width="29.140625" customWidth="1"/>
-    <col min="6" max="6" width="33.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="47.5703125" style="71" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="16.140625" customWidth="1"/>
-    <col min="11" max="11" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="23.42578125" customWidth="1"/>
-    <col min="13" max="13" width="20.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="29.1796875" customWidth="1"/>
+    <col min="6" max="6" width="33.54296875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.1796875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="47.54296875" style="71" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="16.1796875" customWidth="1"/>
+    <col min="11" max="11" width="13.1796875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="23.453125" customWidth="1"/>
+    <col min="13" max="13" width="20.26953125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="17" customWidth="1"/>
-    <col min="15" max="15" width="29.140625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="29.1796875" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="17" customWidth="1"/>
     <col min="17" max="17" width="15" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="17" customWidth="1"/>
-    <col min="19" max="19" width="20.28515625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="20.26953125" bestFit="1" customWidth="1"/>
     <col min="20" max="22" width="17" customWidth="1"/>
     <col min="23" max="23" width="15" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="17" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="17" bestFit="1" customWidth="1"/>
     <col min="27" max="28" width="17" customWidth="1"/>
-    <col min="29" max="29" width="47.140625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="47.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="5:17">
+    <row r="1" spans="5:17" x14ac:dyDescent="0.35">
       <c r="F1" t="s">
         <v>133</v>
       </c>
@@ -9150,7 +9134,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="5:17">
+    <row r="2" spans="5:17" x14ac:dyDescent="0.35">
       <c r="E2">
         <v>1</v>
       </c>
@@ -9189,7 +9173,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="5:17">
+    <row r="3" spans="5:17" x14ac:dyDescent="0.35">
       <c r="E3">
         <v>2</v>
       </c>
@@ -9228,7 +9212,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="5:17">
+    <row r="4" spans="5:17" x14ac:dyDescent="0.35">
       <c r="E4">
         <v>3</v>
       </c>
@@ -9267,7 +9251,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="5:17">
+    <row r="5" spans="5:17" x14ac:dyDescent="0.35">
       <c r="E5">
         <v>4</v>
       </c>
@@ -9300,7 +9284,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="5:17">
+    <row r="6" spans="5:17" x14ac:dyDescent="0.35">
       <c r="E6">
         <v>5</v>
       </c>
@@ -9336,7 +9320,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="5:17">
+    <row r="7" spans="5:17" x14ac:dyDescent="0.35">
       <c r="M7" s="6" t="s">
         <v>154</v>
       </c>
@@ -9357,7 +9341,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="8" spans="5:17">
+    <row r="8" spans="5:17" x14ac:dyDescent="0.35">
       <c r="M8" s="6" t="s">
         <v>155</v>
       </c>
@@ -9378,13 +9362,13 @@
         <v>78</v>
       </c>
     </row>
-    <row r="9" spans="5:17">
+    <row r="9" spans="5:17" x14ac:dyDescent="0.35">
       <c r="M9" s="6"/>
     </row>
-    <row r="10" spans="5:17">
+    <row r="10" spans="5:17" x14ac:dyDescent="0.35">
       <c r="M10" s="6"/>
     </row>
-    <row r="11" spans="5:17">
+    <row r="11" spans="5:17" x14ac:dyDescent="0.35">
       <c r="E11" t="s">
         <v>156</v>
       </c>
@@ -9393,7 +9377,7 @@
       </c>
       <c r="M11" s="6"/>
     </row>
-    <row r="12" spans="5:17">
+    <row r="12" spans="5:17" x14ac:dyDescent="0.35">
       <c r="E12" t="s">
         <v>157</v>
       </c>
@@ -9402,7 +9386,7 @@
       </c>
       <c r="M12" s="60"/>
     </row>
-    <row r="14" spans="5:17">
+    <row r="14" spans="5:17" x14ac:dyDescent="0.35">
       <c r="E14" t="s">
         <v>158</v>
       </c>
@@ -9413,7 +9397,7 @@
         <v>1100</v>
       </c>
     </row>
-    <row r="15" spans="5:17">
+    <row r="15" spans="5:17" x14ac:dyDescent="0.35">
       <c r="E15" t="s">
         <v>159</v>
       </c>
@@ -9424,42 +9408,42 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="21" spans="2:34">
+    <row r="21" spans="2:34" x14ac:dyDescent="0.35">
       <c r="J21" s="58"/>
-      <c r="K21" s="176" t="s">
+      <c r="K21" s="174" t="s">
         <v>160</v>
       </c>
-      <c r="L21" s="177"/>
-      <c r="M21" s="177"/>
-      <c r="N21" s="177"/>
-      <c r="O21" s="177"/>
-      <c r="P21" s="178"/>
-      <c r="Q21" s="176" t="s">
+      <c r="L21" s="175"/>
+      <c r="M21" s="175"/>
+      <c r="N21" s="175"/>
+      <c r="O21" s="175"/>
+      <c r="P21" s="176"/>
+      <c r="Q21" s="174" t="s">
         <v>161</v>
       </c>
-      <c r="R21" s="177"/>
-      <c r="S21" s="177"/>
-      <c r="T21" s="177"/>
-      <c r="U21" s="177"/>
-      <c r="V21" s="178"/>
-      <c r="W21" s="176" t="s">
+      <c r="R21" s="175"/>
+      <c r="S21" s="175"/>
+      <c r="T21" s="175"/>
+      <c r="U21" s="175"/>
+      <c r="V21" s="176"/>
+      <c r="W21" s="174" t="s">
         <v>162</v>
       </c>
-      <c r="X21" s="177"/>
-      <c r="Y21" s="177"/>
-      <c r="Z21" s="177"/>
-      <c r="AA21" s="177"/>
-      <c r="AB21" s="178"/>
-      <c r="AC21" s="179" t="s">
+      <c r="X21" s="175"/>
+      <c r="Y21" s="175"/>
+      <c r="Z21" s="175"/>
+      <c r="AA21" s="175"/>
+      <c r="AB21" s="176"/>
+      <c r="AC21" s="177" t="s">
         <v>163</v>
       </c>
-      <c r="AD21" s="180"/>
-      <c r="AE21" s="180"/>
-      <c r="AF21" s="180"/>
-      <c r="AG21" s="180"/>
-      <c r="AH21" s="180"/>
-    </row>
-    <row r="22" spans="2:34">
+      <c r="AD21" s="178"/>
+      <c r="AE21" s="178"/>
+      <c r="AF21" s="178"/>
+      <c r="AG21" s="178"/>
+      <c r="AH21" s="178"/>
+    </row>
+    <row r="22" spans="2:34" x14ac:dyDescent="0.35">
       <c r="B22" s="87"/>
       <c r="C22" s="89"/>
       <c r="D22" s="87"/>
@@ -9496,7 +9480,7 @@
       <c r="AE22" s="48"/>
       <c r="AF22" s="48"/>
     </row>
-    <row r="23" spans="2:34">
+    <row r="23" spans="2:34" x14ac:dyDescent="0.35">
       <c r="B23" s="87" t="s">
         <v>0</v>
       </c>
@@ -9595,7 +9579,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="24" spans="2:34">
+    <row r="24" spans="2:34" x14ac:dyDescent="0.35">
       <c r="B24" s="6">
         <v>1</v>
       </c>
@@ -9648,7 +9632,7 @@
       <c r="AE24" s="3"/>
       <c r="AF24" s="3"/>
     </row>
-    <row r="25" spans="2:34">
+    <row r="25" spans="2:34" x14ac:dyDescent="0.35">
       <c r="B25" s="6">
         <v>2</v>
       </c>
@@ -9701,7 +9685,7 @@
       <c r="AE25" s="3"/>
       <c r="AF25" s="3"/>
     </row>
-    <row r="26" spans="2:34">
+    <row r="26" spans="2:34" x14ac:dyDescent="0.35">
       <c r="B26" s="6">
         <v>3</v>
       </c>
@@ -9750,7 +9734,7 @@
       <c r="AE26" s="3"/>
       <c r="AF26" s="3"/>
     </row>
-    <row r="27" spans="2:34">
+    <row r="27" spans="2:34" x14ac:dyDescent="0.35">
       <c r="B27" s="6">
         <v>4</v>
       </c>
@@ -9803,7 +9787,7 @@
       <c r="AE27" s="3"/>
       <c r="AF27" s="3"/>
     </row>
-    <row r="28" spans="2:34">
+    <row r="28" spans="2:34" x14ac:dyDescent="0.35">
       <c r="B28" s="6">
         <v>5</v>
       </c>
@@ -9856,7 +9840,7 @@
       <c r="AE28" s="3"/>
       <c r="AF28" s="3"/>
     </row>
-    <row r="29" spans="2:34">
+    <row r="29" spans="2:34" x14ac:dyDescent="0.35">
       <c r="B29" s="6">
         <v>6</v>
       </c>
@@ -9909,7 +9893,7 @@
       <c r="AE29" s="3"/>
       <c r="AF29" s="3"/>
     </row>
-    <row r="30" spans="2:34">
+    <row r="30" spans="2:34" x14ac:dyDescent="0.35">
       <c r="B30" s="6">
         <v>7</v>
       </c>
@@ -9962,7 +9946,7 @@
       <c r="AE30" s="3"/>
       <c r="AF30" s="3"/>
     </row>
-    <row r="31" spans="2:34">
+    <row r="31" spans="2:34" x14ac:dyDescent="0.35">
       <c r="B31" s="6">
         <v>8</v>
       </c>
@@ -10015,7 +9999,7 @@
       <c r="AE31" s="3"/>
       <c r="AF31" s="3"/>
     </row>
-    <row r="32" spans="2:34">
+    <row r="32" spans="2:34" x14ac:dyDescent="0.35">
       <c r="B32" s="6">
         <v>9</v>
       </c>
@@ -10064,7 +10048,7 @@
       <c r="AE32" s="3"/>
       <c r="AF32" s="3"/>
     </row>
-    <row r="33" spans="2:32">
+    <row r="33" spans="2:32" x14ac:dyDescent="0.35">
       <c r="B33" s="6">
         <v>10</v>
       </c>
@@ -10117,7 +10101,7 @@
       <c r="AE33" s="3"/>
       <c r="AF33" s="3"/>
     </row>
-    <row r="34" spans="2:32">
+    <row r="34" spans="2:32" x14ac:dyDescent="0.35">
       <c r="B34" s="6">
         <v>11</v>
       </c>
@@ -10194,7 +10178,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="35" spans="2:32">
+    <row r="35" spans="2:32" x14ac:dyDescent="0.35">
       <c r="B35" s="6">
         <v>12</v>
       </c>
@@ -10243,7 +10227,7 @@
       <c r="AE35" s="3"/>
       <c r="AF35" s="3"/>
     </row>
-    <row r="36" spans="2:32">
+    <row r="36" spans="2:32" x14ac:dyDescent="0.35">
       <c r="B36" s="6">
         <v>13</v>
       </c>
@@ -10292,7 +10276,7 @@
       <c r="AE36" s="3"/>
       <c r="AF36" s="3"/>
     </row>
-    <row r="37" spans="2:32">
+    <row r="37" spans="2:32" x14ac:dyDescent="0.35">
       <c r="B37" s="6">
         <v>14</v>
       </c>
@@ -10341,7 +10325,7 @@
       <c r="AE37" s="3"/>
       <c r="AF37" s="3"/>
     </row>
-    <row r="38" spans="2:32">
+    <row r="38" spans="2:32" x14ac:dyDescent="0.35">
       <c r="B38" s="6">
         <v>15</v>
       </c>
@@ -10390,7 +10374,7 @@
       <c r="AE38" s="3"/>
       <c r="AF38" s="3"/>
     </row>
-    <row r="39" spans="2:32">
+    <row r="39" spans="2:32" x14ac:dyDescent="0.35">
       <c r="B39" s="6">
         <v>17</v>
       </c>
@@ -10439,7 +10423,7 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
     </row>
-    <row r="40" spans="2:32">
+    <row r="40" spans="2:32" x14ac:dyDescent="0.35">
       <c r="B40" s="6">
         <v>18</v>
       </c>
@@ -10488,7 +10472,7 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
     </row>
-    <row r="41" spans="2:32">
+    <row r="41" spans="2:32" x14ac:dyDescent="0.35">
       <c r="B41" s="6">
         <v>19</v>
       </c>
@@ -10537,7 +10521,7 @@
       <c r="AE41" s="3"/>
       <c r="AF41" s="3"/>
     </row>
-    <row r="42" spans="2:32">
+    <row r="42" spans="2:32" x14ac:dyDescent="0.35">
       <c r="B42" s="6">
         <v>20</v>
       </c>
@@ -10586,7 +10570,7 @@
       <c r="AE42" s="3"/>
       <c r="AF42" s="3"/>
     </row>
-    <row r="43" spans="2:32">
+    <row r="43" spans="2:32" x14ac:dyDescent="0.35">
       <c r="B43" s="6">
         <v>21</v>
       </c>
@@ -10635,7 +10619,7 @@
       <c r="AE43" s="3"/>
       <c r="AF43" s="3"/>
     </row>
-    <row r="44" spans="2:32">
+    <row r="44" spans="2:32" x14ac:dyDescent="0.35">
       <c r="B44" s="6">
         <v>22</v>
       </c>
@@ -10684,7 +10668,7 @@
       <c r="AE44" s="3"/>
       <c r="AF44" s="3"/>
     </row>
-    <row r="45" spans="2:32">
+    <row r="45" spans="2:32" x14ac:dyDescent="0.35">
       <c r="B45" s="6">
         <v>23</v>
       </c>
@@ -10733,7 +10717,7 @@
       <c r="AE45" s="3"/>
       <c r="AF45" s="3"/>
     </row>
-    <row r="46" spans="2:32">
+    <row r="46" spans="2:32" x14ac:dyDescent="0.35">
       <c r="B46" s="6">
         <v>24</v>
       </c>
@@ -10782,7 +10766,7 @@
       <c r="AE46" s="3"/>
       <c r="AF46" s="3"/>
     </row>
-    <row r="47" spans="2:32">
+    <row r="47" spans="2:32" x14ac:dyDescent="0.35">
       <c r="B47" s="6">
         <v>25</v>
       </c>
@@ -10831,7 +10815,7 @@
       <c r="AE47" s="3"/>
       <c r="AF47" s="3"/>
     </row>
-    <row r="48" spans="2:32">
+    <row r="48" spans="2:32" x14ac:dyDescent="0.35">
       <c r="B48" s="6">
         <v>26</v>
       </c>
@@ -10880,7 +10864,7 @@
       <c r="AE48" s="3"/>
       <c r="AF48" s="3"/>
     </row>
-    <row r="49" spans="2:32">
+    <row r="49" spans="2:32" x14ac:dyDescent="0.35">
       <c r="B49" s="6">
         <v>27</v>
       </c>
@@ -10929,7 +10913,7 @@
       <c r="AE49" s="3"/>
       <c r="AF49" s="3"/>
     </row>
-    <row r="50" spans="2:32">
+    <row r="50" spans="2:32" x14ac:dyDescent="0.35">
       <c r="B50" s="6">
         <v>28</v>
       </c>
@@ -10978,7 +10962,7 @@
       <c r="AE50" s="3"/>
       <c r="AF50" s="3"/>
     </row>
-    <row r="51" spans="2:32">
+    <row r="51" spans="2:32" x14ac:dyDescent="0.35">
       <c r="B51" s="6">
         <v>29</v>
       </c>
@@ -11031,7 +11015,7 @@
       <c r="AE51" s="3"/>
       <c r="AF51" s="3"/>
     </row>
-    <row r="52" spans="2:32">
+    <row r="52" spans="2:32" x14ac:dyDescent="0.35">
       <c r="B52" s="6">
         <v>30</v>
       </c>
@@ -11084,7 +11068,7 @@
       <c r="AE52" s="3"/>
       <c r="AF52" s="3"/>
     </row>
-    <row r="53" spans="2:32">
+    <row r="53" spans="2:32" x14ac:dyDescent="0.35">
       <c r="B53" s="6">
         <v>31</v>
       </c>
@@ -11139,7 +11123,7 @@
       <c r="AE53" s="3"/>
       <c r="AF53" s="3"/>
     </row>
-    <row r="54" spans="2:32">
+    <row r="54" spans="2:32" x14ac:dyDescent="0.35">
       <c r="B54" s="6">
         <v>32</v>
       </c>
@@ -11192,7 +11176,7 @@
       <c r="AE54" s="3"/>
       <c r="AF54" s="3"/>
     </row>
-    <row r="55" spans="2:32">
+    <row r="55" spans="2:32" x14ac:dyDescent="0.35">
       <c r="B55" s="6">
         <v>33</v>
       </c>
@@ -11241,7 +11225,7 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
     </row>
-    <row r="56" spans="2:32">
+    <row r="56" spans="2:32" x14ac:dyDescent="0.35">
       <c r="B56" s="6">
         <v>34</v>
       </c>
@@ -11290,7 +11274,7 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
     </row>
-    <row r="57" spans="2:32">
+    <row r="57" spans="2:32" x14ac:dyDescent="0.35">
       <c r="B57" s="6">
         <v>35</v>
       </c>
@@ -11339,7 +11323,7 @@
       <c r="AE57" s="3"/>
       <c r="AF57" s="3"/>
     </row>
-    <row r="58" spans="2:32">
+    <row r="58" spans="2:32" x14ac:dyDescent="0.35">
       <c r="B58" s="6">
         <v>36</v>
       </c>
@@ -11392,7 +11376,7 @@
       <c r="AE58" s="3"/>
       <c r="AF58" s="3"/>
     </row>
-    <row r="59" spans="2:32">
+    <row r="59" spans="2:32" x14ac:dyDescent="0.35">
       <c r="B59" s="6">
         <v>37</v>
       </c>
@@ -11441,7 +11425,7 @@
       <c r="AE59" s="3"/>
       <c r="AF59" s="3"/>
     </row>
-    <row r="60" spans="2:32">
+    <row r="60" spans="2:32" x14ac:dyDescent="0.35">
       <c r="B60" s="6">
         <v>38</v>
       </c>
@@ -11490,7 +11474,7 @@
       <c r="AE60" s="3"/>
       <c r="AF60" s="3"/>
     </row>
-    <row r="61" spans="2:32">
+    <row r="61" spans="2:32" x14ac:dyDescent="0.35">
       <c r="B61" s="6">
         <v>39</v>
       </c>
@@ -11553,7 +11537,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="62" spans="2:32">
+    <row r="62" spans="2:32" x14ac:dyDescent="0.35">
       <c r="B62" s="6">
         <v>40</v>
       </c>
@@ -11606,7 +11590,7 @@
       <c r="AE62" s="3"/>
       <c r="AF62" s="3"/>
     </row>
-    <row r="63" spans="2:32">
+    <row r="63" spans="2:32" x14ac:dyDescent="0.35">
       <c r="B63" s="6">
         <v>41</v>
       </c>
@@ -11659,7 +11643,7 @@
       <c r="AE63" s="3"/>
       <c r="AF63" s="3"/>
     </row>
-    <row r="64" spans="2:32">
+    <row r="64" spans="2:32" x14ac:dyDescent="0.35">
       <c r="B64" s="6">
         <v>42</v>
       </c>
@@ -11712,7 +11696,7 @@
       <c r="AE64" s="3"/>
       <c r="AF64" s="3"/>
     </row>
-    <row r="65" spans="2:32">
+    <row r="65" spans="2:32" x14ac:dyDescent="0.35">
       <c r="B65" s="6">
         <v>43</v>
       </c>
@@ -11761,7 +11745,7 @@
       <c r="AE65" s="3"/>
       <c r="AF65" s="3"/>
     </row>
-    <row r="66" spans="2:32">
+    <row r="66" spans="2:32" x14ac:dyDescent="0.35">
       <c r="B66" s="6">
         <v>44</v>
       </c>
@@ -11810,7 +11794,7 @@
       <c r="AE66" s="3"/>
       <c r="AF66" s="3"/>
     </row>
-    <row r="67" spans="2:32">
+    <row r="67" spans="2:32" x14ac:dyDescent="0.35">
       <c r="B67" s="6">
         <v>45</v>
       </c>
@@ -11859,7 +11843,7 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
     </row>
-    <row r="68" spans="2:32">
+    <row r="68" spans="2:32" x14ac:dyDescent="0.35">
       <c r="B68" s="6">
         <v>46</v>
       </c>
@@ -11908,7 +11892,7 @@
       <c r="AE68" s="3"/>
       <c r="AF68" s="3"/>
     </row>
-    <row r="69" spans="2:32">
+    <row r="69" spans="2:32" x14ac:dyDescent="0.35">
       <c r="B69" s="6">
         <v>47</v>
       </c>
@@ -11961,7 +11945,7 @@
       <c r="AE69" s="3"/>
       <c r="AF69" s="3"/>
     </row>
-    <row r="70" spans="2:32">
+    <row r="70" spans="2:32" x14ac:dyDescent="0.35">
       <c r="B70" s="6">
         <v>48</v>
       </c>
@@ -12010,7 +11994,7 @@
       <c r="AE70" s="3"/>
       <c r="AF70" s="3"/>
     </row>
-    <row r="71" spans="2:32">
+    <row r="71" spans="2:32" x14ac:dyDescent="0.35">
       <c r="B71" s="6">
         <v>49</v>
       </c>
@@ -12059,7 +12043,7 @@
       <c r="AE71" s="3"/>
       <c r="AF71" s="3"/>
     </row>
-    <row r="72" spans="2:32">
+    <row r="72" spans="2:32" x14ac:dyDescent="0.35">
       <c r="B72" s="6">
         <v>50</v>
       </c>
@@ -12112,7 +12096,7 @@
       <c r="AE72" s="3"/>
       <c r="AF72" s="3"/>
     </row>
-    <row r="73" spans="2:32" ht="15.6">
+    <row r="73" spans="2:32" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B73" s="6">
         <v>51</v>
       </c>
@@ -12165,7 +12149,7 @@
       <c r="AE73" s="3"/>
       <c r="AF73" s="3"/>
     </row>
-    <row r="74" spans="2:32">
+    <row r="74" spans="2:32" x14ac:dyDescent="0.35">
       <c r="B74" s="6">
         <v>52</v>
       </c>
@@ -12218,7 +12202,7 @@
       <c r="AE74" s="3"/>
       <c r="AF74" s="3"/>
     </row>
-    <row r="75" spans="2:32">
+    <row r="75" spans="2:32" x14ac:dyDescent="0.35">
       <c r="B75" s="6">
         <v>53</v>
       </c>
@@ -12271,7 +12255,7 @@
       <c r="AE75" s="3"/>
       <c r="AF75" s="3"/>
     </row>
-    <row r="76" spans="2:32">
+    <row r="76" spans="2:32" x14ac:dyDescent="0.35">
       <c r="B76" s="6">
         <v>54</v>
       </c>
@@ -12324,7 +12308,7 @@
       <c r="AE76" s="3"/>
       <c r="AF76" s="3"/>
     </row>
-    <row r="77" spans="2:32">
+    <row r="77" spans="2:32" x14ac:dyDescent="0.35">
       <c r="B77" s="6">
         <v>55</v>
       </c>
@@ -12377,7 +12361,7 @@
       <c r="AE77" s="3"/>
       <c r="AF77" s="3"/>
     </row>
-    <row r="78" spans="2:32">
+    <row r="78" spans="2:32" x14ac:dyDescent="0.35">
       <c r="B78" s="6">
         <v>56</v>
       </c>
@@ -12426,7 +12410,7 @@
       <c r="AE78" s="3"/>
       <c r="AF78" s="3"/>
     </row>
-    <row r="79" spans="2:32">
+    <row r="79" spans="2:32" x14ac:dyDescent="0.35">
       <c r="B79" s="6">
         <v>57</v>
       </c>
@@ -12475,7 +12459,7 @@
       <c r="AE79" s="3"/>
       <c r="AF79" s="3"/>
     </row>
-    <row r="80" spans="2:32">
+    <row r="80" spans="2:32" x14ac:dyDescent="0.35">
       <c r="B80" s="6">
         <v>58</v>
       </c>
@@ -12528,7 +12512,7 @@
       <c r="AE80" s="3"/>
       <c r="AF80" s="3"/>
     </row>
-    <row r="81" spans="2:32">
+    <row r="81" spans="2:32" x14ac:dyDescent="0.35">
       <c r="B81" s="6">
         <v>59</v>
       </c>
@@ -12581,7 +12565,7 @@
       <c r="AE81" s="3"/>
       <c r="AF81" s="3"/>
     </row>
-    <row r="82" spans="2:32">
+    <row r="82" spans="2:32" x14ac:dyDescent="0.35">
       <c r="B82" s="6">
         <v>60</v>
       </c>
@@ -12630,7 +12614,7 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
     </row>
-    <row r="83" spans="2:32">
+    <row r="83" spans="2:32" x14ac:dyDescent="0.35">
       <c r="B83" s="6">
         <v>61</v>
       </c>
@@ -12679,7 +12663,7 @@
       <c r="AE83" s="3"/>
       <c r="AF83" s="3"/>
     </row>
-    <row r="84" spans="2:32">
+    <row r="84" spans="2:32" x14ac:dyDescent="0.35">
       <c r="B84" s="6">
         <v>62</v>
       </c>
@@ -12732,7 +12716,7 @@
       <c r="AE84" s="3"/>
       <c r="AF84" s="3"/>
     </row>
-    <row r="85" spans="2:32">
+    <row r="85" spans="2:32" x14ac:dyDescent="0.35">
       <c r="B85" s="6">
         <v>63</v>
       </c>
@@ -12785,7 +12769,7 @@
       <c r="AE85" s="3"/>
       <c r="AF85" s="3"/>
     </row>
-    <row r="86" spans="2:32">
+    <row r="86" spans="2:32" x14ac:dyDescent="0.35">
       <c r="B86" s="6">
         <v>64</v>
       </c>
@@ -12834,7 +12818,7 @@
       <c r="AE86" s="3"/>
       <c r="AF86" s="3"/>
     </row>
-    <row r="87" spans="2:32">
+    <row r="87" spans="2:32" x14ac:dyDescent="0.35">
       <c r="B87" s="6">
         <v>65</v>
       </c>
@@ -12883,7 +12867,7 @@
       <c r="AE87" s="3"/>
       <c r="AF87" s="3"/>
     </row>
-    <row r="88" spans="2:32">
+    <row r="88" spans="2:32" x14ac:dyDescent="0.35">
       <c r="B88" s="6">
         <v>66</v>
       </c>
@@ -12936,7 +12920,7 @@
       <c r="AE88" s="3"/>
       <c r="AF88" s="3"/>
     </row>
-    <row r="89" spans="2:32">
+    <row r="89" spans="2:32" x14ac:dyDescent="0.35">
       <c r="B89" s="6">
         <v>67</v>
       </c>
@@ -12989,7 +12973,7 @@
       <c r="AE89" s="3"/>
       <c r="AF89" s="3"/>
     </row>
-    <row r="90" spans="2:32">
+    <row r="90" spans="2:32" x14ac:dyDescent="0.35">
       <c r="B90" s="6">
         <v>68</v>
       </c>
@@ -13042,7 +13026,7 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
     </row>
-    <row r="91" spans="2:32">
+    <row r="91" spans="2:32" x14ac:dyDescent="0.35">
       <c r="B91" s="6">
         <v>69</v>
       </c>
@@ -13095,7 +13079,7 @@
       <c r="AE91" s="3"/>
       <c r="AF91" s="3"/>
     </row>
-    <row r="92" spans="2:32">
+    <row r="92" spans="2:32" x14ac:dyDescent="0.35">
       <c r="B92" s="6">
         <v>70</v>
       </c>
@@ -13148,7 +13132,7 @@
       <c r="AE92" s="3"/>
       <c r="AF92" s="3"/>
     </row>
-    <row r="93" spans="2:32">
+    <row r="93" spans="2:32" x14ac:dyDescent="0.35">
       <c r="B93" s="6">
         <v>71</v>
       </c>
@@ -13201,7 +13185,7 @@
       <c r="AE93" s="3"/>
       <c r="AF93" s="3"/>
     </row>
-    <row r="94" spans="2:32">
+    <row r="94" spans="2:32" x14ac:dyDescent="0.35">
       <c r="B94" s="6">
         <v>72</v>
       </c>
@@ -13250,7 +13234,7 @@
       <c r="AE94" s="3"/>
       <c r="AF94" s="3"/>
     </row>
-    <row r="95" spans="2:32">
+    <row r="95" spans="2:32" x14ac:dyDescent="0.35">
       <c r="B95" s="6">
         <v>73</v>
       </c>
@@ -13299,7 +13283,7 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
     </row>
-    <row r="96" spans="2:32">
+    <row r="96" spans="2:32" x14ac:dyDescent="0.35">
       <c r="B96" s="6">
         <v>74</v>
       </c>
@@ -13348,7 +13332,7 @@
       <c r="AE96" s="3"/>
       <c r="AF96" s="3"/>
     </row>
-    <row r="97" spans="2:32">
+    <row r="97" spans="2:32" x14ac:dyDescent="0.35">
       <c r="B97" s="6">
         <v>75</v>
       </c>
@@ -13397,7 +13381,7 @@
       <c r="AE97" s="3"/>
       <c r="AF97" s="3"/>
     </row>
-    <row r="98" spans="2:32">
+    <row r="98" spans="2:32" x14ac:dyDescent="0.35">
       <c r="B98" s="6">
         <v>76</v>
       </c>
@@ -13446,7 +13430,7 @@
       <c r="AE98" s="3"/>
       <c r="AF98" s="3"/>
     </row>
-    <row r="99" spans="2:32">
+    <row r="99" spans="2:32" x14ac:dyDescent="0.35">
       <c r="B99" s="6">
         <v>77</v>
       </c>
@@ -13495,7 +13479,7 @@
       <c r="AE99" s="3"/>
       <c r="AF99" s="3"/>
     </row>
-    <row r="100" spans="2:32">
+    <row r="100" spans="2:32" x14ac:dyDescent="0.35">
       <c r="B100" s="6">
         <v>78</v>
       </c>
@@ -13521,7 +13505,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="101" spans="2:32">
+    <row r="101" spans="2:32" x14ac:dyDescent="0.35">
       <c r="B101" s="6">
         <v>79</v>
       </c>
@@ -13565,14 +13549,14 @@
     <tabColor rgb="FF92D050"/>
   </sheetPr>
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="8.7109375" style="71"/>
-    <col min="2" max="2" width="32.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="60.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.7265625" style="71"/>
+    <col min="2" max="2" width="32.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="60.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="48" t="s">
         <v>216</v>
       </c>
@@ -13583,7 +13567,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="73">
         <v>1</v>
       </c>
@@ -13594,7 +13578,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" s="73">
         <v>2</v>
       </c>
@@ -13605,7 +13589,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="72.599999999999994">
+    <row r="4" spans="1:3" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A4" s="15">
         <v>3</v>
       </c>
@@ -13616,7 +13600,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="48" t="s">
         <v>216</v>
       </c>
@@ -13627,7 +13611,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="73">
         <v>1</v>
       </c>
@@ -13636,7 +13620,7 @@
       </c>
       <c r="C8" s="3"/>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="73">
         <v>2</v>
       </c>
@@ -13654,28 +13638,28 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{106600C0-B441-459A-91DA-48A6163B82F3}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:E33"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="23.85546875" customWidth="1"/>
-    <col min="2" max="2" width="25.140625" customWidth="1"/>
-    <col min="3" max="3" width="39.42578125" customWidth="1"/>
-    <col min="4" max="4" width="16.85546875" style="71" customWidth="1"/>
-    <col min="5" max="5" width="31.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.81640625" customWidth="1"/>
+    <col min="2" max="2" width="25.1796875" customWidth="1"/>
+    <col min="3" max="3" width="39.453125" customWidth="1"/>
+    <col min="4" max="4" width="16.81640625" style="71" customWidth="1"/>
+    <col min="5" max="5" width="31.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="23.45">
+    <row r="1" spans="1:5" ht="23.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="36" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
-      <c r="A2" s="181" t="s">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2" s="179" t="s">
         <v>228</v>
       </c>
-      <c r="B2" s="181"/>
+      <c r="B2" s="179"/>
       <c r="C2" s="100"/>
     </row>
-    <row r="3" spans="1:5" s="1" customFormat="1" ht="29.1">
+    <row r="3" spans="1:5" s="1" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A3" s="53"/>
       <c r="B3" s="53"/>
       <c r="C3" s="101" t="s">
@@ -13683,7 +13667,7 @@
       </c>
       <c r="D3" s="99"/>
     </row>
-    <row r="4" spans="1:5" s="103" customFormat="1" ht="60" customHeight="1">
+    <row r="4" spans="1:5" s="103" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="28" t="s">
         <v>230</v>
       </c>
@@ -13700,7 +13684,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="29.1">
+    <row r="5" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
         <v>174</v>
       </c>
@@ -13717,7 +13701,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" s="43" t="s">
         <v>238</v>
       </c>
@@ -13734,7 +13718,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
         <v>240</v>
       </c>
@@ -13751,7 +13735,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" s="43" t="s">
         <v>244</v>
       </c>
@@ -13768,7 +13752,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="9" spans="1:5" hidden="1">
+    <row r="9" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
         <v>13</v>
       </c>
@@ -13779,7 +13763,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="10" spans="1:5" hidden="1">
+    <row r="10" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
         <v>16</v>
       </c>
@@ -13788,7 +13772,7 @@
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" s="43" t="s">
         <v>248</v>
       </c>
@@ -13805,7 +13789,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="15" customHeight="1">
+    <row r="12" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
         <v>17</v>
       </c>
@@ -13822,7 +13806,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="15" customHeight="1">
+    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
         <v>20</v>
       </c>
@@ -13839,7 +13823,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="43.5">
+    <row r="14" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A14" s="43" t="s">
         <v>254</v>
       </c>
@@ -13856,7 +13840,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="15" customHeight="1">
+    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
         <v>24</v>
       </c>
@@ -13873,7 +13857,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="43.5">
+    <row r="16" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A16" s="3" t="s">
         <v>258</v>
       </c>
@@ -13890,7 +13874,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="15" hidden="1" customHeight="1">
+    <row r="17" spans="1:5" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="3" t="s">
         <v>261</v>
       </c>
@@ -13901,7 +13885,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" s="3" t="s">
         <v>263</v>
       </c>
@@ -13918,7 +13902,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" s="3" t="s">
         <v>266</v>
       </c>
@@ -13935,7 +13919,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20" s="43" t="s">
         <v>268</v>
       </c>
@@ -13952,7 +13936,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="21" spans="1:5">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21" s="43" t="s">
         <v>271</v>
       </c>
@@ -13969,7 +13953,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="22" spans="1:5">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22" s="3" t="s">
         <v>22</v>
       </c>
@@ -13986,7 +13970,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="23" spans="1:5">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23" s="3" t="s">
         <v>26</v>
       </c>
@@ -14003,7 +13987,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="29.1">
+    <row r="24" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A24" s="3" t="s">
         <v>275</v>
       </c>
@@ -14020,7 +14004,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="25" spans="1:5">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A25" s="3" t="s">
         <v>277</v>
       </c>
@@ -14037,7 +14021,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="26" spans="1:5" hidden="1">
+    <row r="26" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A26" s="3" t="s">
         <v>279</v>
       </c>
@@ -14048,7 +14032,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="27" spans="1:5">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A27" s="3" t="s">
         <v>280</v>
       </c>
@@ -14065,7 +14049,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="28" spans="1:5">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A28" s="3" t="s">
         <v>281</v>
       </c>
@@ -14082,7 +14066,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="29" spans="1:5">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A29" s="43" t="s">
         <v>283</v>
       </c>
@@ -14099,7 +14083,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="30" spans="1:5">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A30" s="43" t="s">
         <v>284</v>
       </c>
@@ -14116,7 +14100,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="31" spans="1:5" hidden="1">
+    <row r="31" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A31" s="3" t="s">
         <v>286</v>
       </c>
@@ -14127,7 +14111,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="32" spans="1:5" hidden="1">
+    <row r="32" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A32" s="3" t="s">
         <v>288</v>
       </c>
@@ -14138,7 +14122,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="33" spans="1:5" hidden="1">
+    <row r="33" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A33" s="3" t="s">
         <v>290</v>
       </c>
@@ -14174,19 +14158,19 @@
   <sheetPr>
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
-  <dimension ref="A1:J20"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <dimension ref="A1:J19"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="33.5703125" customWidth="1"/>
-    <col min="3" max="6" width="44.140625" customWidth="1"/>
-    <col min="7" max="7" width="43.7109375" customWidth="1"/>
-    <col min="8" max="8" width="32.42578125" customWidth="1"/>
-    <col min="9" max="9" width="29.140625" style="71" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="29.42578125" customWidth="1"/>
+    <col min="1" max="1" width="11.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="33.54296875" customWidth="1"/>
+    <col min="3" max="6" width="44.1796875" customWidth="1"/>
+    <col min="7" max="7" width="43.7265625" customWidth="1"/>
+    <col min="8" max="8" width="32.453125" customWidth="1"/>
+    <col min="9" max="9" width="29.1796875" style="71" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="29.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="23.45">
+    <row r="1" spans="1:10" ht="23.5" x14ac:dyDescent="0.55000000000000004">
       <c r="B1" s="112"/>
       <c r="C1" s="3"/>
       <c r="D1" s="3"/>
@@ -14196,11 +14180,11 @@
       <c r="H1" s="3"/>
       <c r="I1" s="73"/>
     </row>
-    <row r="2" spans="1:10">
-      <c r="B2" s="182" t="s">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="B2" s="180" t="s">
         <v>228</v>
       </c>
-      <c r="C2" s="182"/>
+      <c r="C2" s="180"/>
       <c r="D2" s="113"/>
       <c r="E2" s="113"/>
       <c r="F2" s="113"/>
@@ -14208,7 +14192,7 @@
       <c r="H2" s="48"/>
       <c r="I2" s="73"/>
     </row>
-    <row r="3" spans="1:10" ht="32.450000000000003" customHeight="1">
+    <row r="3" spans="1:10" ht="32.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B3" s="123"/>
       <c r="C3" s="123"/>
       <c r="D3" s="123"/>
@@ -14218,33 +14202,33 @@
       <c r="H3" s="62"/>
       <c r="I3" s="124"/>
     </row>
-    <row r="4" spans="1:10" ht="32.450000000000003" customHeight="1">
-      <c r="A4" s="183" t="s">
+    <row r="4" spans="1:10" ht="32.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="181" t="s">
         <v>291</v>
       </c>
-      <c r="B4" s="183"/>
-      <c r="C4" s="183"/>
-      <c r="D4" s="183"/>
-      <c r="E4" s="183"/>
-      <c r="F4" s="183"/>
-      <c r="G4" s="183"/>
-      <c r="H4" s="183"/>
+      <c r="B4" s="181"/>
+      <c r="C4" s="181"/>
+      <c r="D4" s="181"/>
+      <c r="E4" s="181"/>
+      <c r="F4" s="181"/>
+      <c r="G4" s="181"/>
+      <c r="H4" s="181"/>
       <c r="I4" s="125"/>
     </row>
-    <row r="5" spans="1:10" s="1" customFormat="1" ht="30" customHeight="1">
-      <c r="A5" s="183" t="s">
+    <row r="5" spans="1:10" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="181" t="s">
         <v>292</v>
       </c>
-      <c r="B5" s="183"/>
-      <c r="C5" s="183"/>
-      <c r="D5" s="183"/>
-      <c r="E5" s="183"/>
-      <c r="F5" s="183"/>
-      <c r="G5" s="183"/>
-      <c r="H5" s="183"/>
+      <c r="B5" s="181"/>
+      <c r="C5" s="181"/>
+      <c r="D5" s="181"/>
+      <c r="E5" s="181"/>
+      <c r="F5" s="181"/>
+      <c r="G5" s="181"/>
+      <c r="H5" s="181"/>
       <c r="I5" s="125"/>
     </row>
-    <row r="6" spans="1:10" s="103" customFormat="1" ht="15.6">
+    <row r="6" spans="1:10" s="103" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A6" s="28" t="s">
         <v>293</v>
       </c>
@@ -14273,7 +14257,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="91.5">
+    <row r="7" spans="1:10" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A7" s="6" t="s">
         <v>299</v>
       </c>
@@ -14302,7 +14286,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="43.5">
+    <row r="8" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A8" s="6" t="s">
         <v>304</v>
       </c>
@@ -14331,7 +14315,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9" s="6" t="s">
         <v>310</v>
       </c>
@@ -14358,7 +14342,7 @@
       </c>
       <c r="I9" s="8"/>
     </row>
-    <row r="10" spans="1:10" ht="106.5">
+    <row r="10" spans="1:10" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A10" s="6" t="s">
         <v>313</v>
       </c>
@@ -14388,7 +14372,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="57.95">
+    <row r="11" spans="1:10" ht="58" x14ac:dyDescent="0.35">
       <c r="A11" s="6" t="s">
         <v>317</v>
       </c>
@@ -14415,7 +14399,7 @@
       </c>
       <c r="I11" s="15"/>
     </row>
-    <row r="12" spans="1:10" ht="43.5">
+    <row r="12" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A12" s="6" t="s">
         <v>319</v>
       </c>
@@ -14444,7 +14428,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="29.1">
+    <row r="13" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A13" s="6" t="s">
         <v>323</v>
       </c>
@@ -14471,7 +14455,7 @@
       </c>
       <c r="I13" s="15"/>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A14" s="6" t="s">
         <v>327</v>
       </c>
@@ -14496,7 +14480,7 @@
       </c>
       <c r="I14" s="72"/>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A15" s="6" t="s">
         <v>328</v>
       </c>
@@ -14525,7 +14509,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="43.5">
+    <row r="16" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A16" s="6" t="s">
         <v>331</v>
       </c>
@@ -14548,7 +14532,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="17" spans="1:9">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A17" s="6" t="s">
         <v>335</v>
       </c>
@@ -14569,10 +14553,9 @@
       </c>
       <c r="I17" s="15"/>
     </row>
-    <row r="19" spans="1:9">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B19" s="156"/>
     </row>
-    <row r="20" spans="1:9" ht="15"/>
   </sheetData>
   <autoFilter ref="B6:C17" xr:uid="{00000000-0001-0000-0900-000000000000}"/>
   <mergeCells count="3">
@@ -14596,65 +14579,65 @@
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
   <dimension ref="A1:L19"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="34" customWidth="1"/>
-    <col min="4" max="4" width="21.5703125" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="21.85546875" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="17.85546875" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="43.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.140625" customWidth="1"/>
+    <col min="4" max="4" width="21.54296875" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="21.81640625" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="17.81640625" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="43.81640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.1796875" customWidth="1"/>
     <col min="9" max="9" width="29" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.140625" customWidth="1"/>
-    <col min="11" max="11" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.140625" customWidth="1"/>
+    <col min="10" max="10" width="10.1796875" customWidth="1"/>
+    <col min="11" max="11" width="15.26953125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="23.45">
+    <row r="1" spans="1:12" ht="23.5" x14ac:dyDescent="0.35">
       <c r="B1" s="37"/>
     </row>
-    <row r="2" spans="1:12" ht="56.45" customHeight="1">
-      <c r="B2" s="184" t="s">
+    <row r="2" spans="1:12" ht="56.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B2" s="182" t="s">
         <v>338</v>
       </c>
-      <c r="C2" s="184"/>
-      <c r="D2" s="171"/>
-      <c r="E2" s="171"/>
-      <c r="F2" s="171"/>
-    </row>
-    <row r="3" spans="1:12" ht="56.45" customHeight="1">
+      <c r="C2" s="182"/>
+      <c r="D2" s="172"/>
+      <c r="E2" s="172"/>
+      <c r="F2" s="172"/>
+    </row>
+    <row r="3" spans="1:12" ht="56.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B3" s="126"/>
       <c r="C3" s="126"/>
       <c r="D3" s="62"/>
       <c r="E3" s="62"/>
       <c r="F3" s="62"/>
     </row>
-    <row r="4" spans="1:12">
-      <c r="A4" s="183" t="s">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A4" s="181" t="s">
         <v>339</v>
       </c>
-      <c r="B4" s="183"/>
-      <c r="C4" s="183"/>
-      <c r="D4" s="183"/>
-      <c r="E4" s="183"/>
-      <c r="F4" s="183"/>
-      <c r="G4" s="183"/>
-      <c r="H4" s="183"/>
-    </row>
-    <row r="5" spans="1:12" s="35" customFormat="1" ht="69.95" customHeight="1">
-      <c r="A5" s="183" t="s">
+      <c r="B4" s="181"/>
+      <c r="C4" s="181"/>
+      <c r="D4" s="181"/>
+      <c r="E4" s="181"/>
+      <c r="F4" s="181"/>
+      <c r="G4" s="181"/>
+      <c r="H4" s="181"/>
+    </row>
+    <row r="5" spans="1:12" s="35" customFormat="1" ht="70" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="181" t="s">
         <v>340</v>
       </c>
-      <c r="B5" s="183"/>
-      <c r="C5" s="183"/>
-      <c r="D5" s="183"/>
-      <c r="E5" s="183"/>
-      <c r="F5" s="183"/>
-      <c r="G5" s="183"/>
-      <c r="H5" s="183"/>
-    </row>
-    <row r="6" spans="1:12" s="40" customFormat="1" ht="30.95">
+      <c r="B5" s="181"/>
+      <c r="C5" s="181"/>
+      <c r="D5" s="181"/>
+      <c r="E5" s="181"/>
+      <c r="F5" s="181"/>
+      <c r="G5" s="181"/>
+      <c r="H5" s="181"/>
+    </row>
+    <row r="6" spans="1:12" s="40" customFormat="1" ht="31" x14ac:dyDescent="0.35">
       <c r="A6" s="28" t="s">
         <v>293</v>
       </c>
@@ -14683,7 +14666,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="87">
+    <row r="7" spans="1:12" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A7" s="6" t="s">
         <v>341</v>
       </c>
@@ -14710,7 +14693,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="8" spans="1:12">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A8" s="6" t="s">
         <v>346</v>
       </c>
@@ -14735,7 +14718,7 @@
       </c>
       <c r="I8" s="3"/>
     </row>
-    <row r="9" spans="1:12" ht="72.599999999999994">
+    <row r="9" spans="1:12" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A9" s="6" t="s">
         <v>348</v>
       </c>
@@ -14768,7 +14751,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="72.599999999999994">
+    <row r="10" spans="1:12" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A10" s="6" t="s">
         <v>354</v>
       </c>
@@ -14806,7 +14789,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="29.45" thickBot="1">
+    <row r="11" spans="1:12" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A11" s="6" t="s">
         <v>361</v>
       </c>
@@ -14825,7 +14808,7 @@
       </c>
       <c r="I11" s="3"/>
     </row>
-    <row r="12" spans="1:12">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
       <c r="C12" s="1"/>
       <c r="K12" s="118" t="s">
         <v>364</v>
@@ -14834,7 +14817,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="13" spans="1:12">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
       <c r="K13" s="11" t="s">
         <v>366</v>
       </c>
@@ -14842,41 +14825,41 @@
         <v>367</v>
       </c>
     </row>
-    <row r="14" spans="1:12">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
       <c r="K14" s="11"/>
       <c r="L14" s="12" t="s">
         <v>368</v>
       </c>
     </row>
-    <row r="15" spans="1:12">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
       <c r="K15" s="11"/>
       <c r="L15" s="12" t="s">
         <v>369</v>
       </c>
     </row>
-    <row r="16" spans="1:12">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
       <c r="K16" s="11"/>
       <c r="L16" s="12" t="s">
         <v>370</v>
       </c>
     </row>
-    <row r="17" spans="11:12">
+    <row r="17" spans="11:12" x14ac:dyDescent="0.35">
       <c r="K17" s="11"/>
       <c r="L17" s="12" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="18" spans="11:12" ht="15" thickBot="1">
+    <row r="18" spans="11:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="K18" s="13"/>
       <c r="L18" s="14" t="s">
         <v>372</v>
       </c>
     </row>
-    <row r="19" spans="11:12" ht="15" thickBot="1">
-      <c r="K19" s="185" t="s">
+    <row r="19" spans="11:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="K19" s="183" t="s">
         <v>373</v>
       </c>
-      <c r="L19" s="186"/>
+      <c r="L19" s="184"/>
     </row>
   </sheetData>
   <autoFilter ref="D6:F6" xr:uid="{00000000-0001-0000-0C00-000000000000}"/>
@@ -14885,7 +14868,7 @@
       <selection sqref="A1:K1"/>
       <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
       <pageSetup orientation="portrait" r:id="rId1"/>
-      <autoFilter ref="A2:P11" xr:uid="{BCA4697D-6602-4934-9CAA-B444D1CFE432}"/>
+      <autoFilter ref="A2:P11" xr:uid="{EB255A04-2606-4BD1-9866-2FCFFA079BE9}"/>
     </customSheetView>
   </customSheetViews>
   <mergeCells count="5">
@@ -14913,63 +14896,63 @@
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
   <dimension ref="A1:I42"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="19.140625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="28.140625" customWidth="1"/>
-    <col min="4" max="4" width="21.140625" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="31.28515625" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="11.85546875" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="37.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.28515625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="31.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.1796875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="28.1796875" customWidth="1"/>
+    <col min="4" max="4" width="21.1796875" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="31.26953125" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="11.81640625" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="37.81640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.26953125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="31.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="23.45">
+    <row r="1" spans="1:9" ht="23.5" x14ac:dyDescent="0.55000000000000004">
       <c r="B1" s="132"/>
     </row>
-    <row r="2" spans="1:9" ht="18.600000000000001" customHeight="1">
-      <c r="B2" s="189" t="s">
+    <row r="2" spans="1:9" ht="18.649999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B2" s="187" t="s">
         <v>374</v>
       </c>
-      <c r="C2" s="190"/>
-      <c r="D2" s="171"/>
-      <c r="E2" s="171"/>
-      <c r="F2" s="171"/>
-    </row>
-    <row r="3" spans="1:9" ht="18.600000000000001" customHeight="1">
+      <c r="C2" s="188"/>
+      <c r="D2" s="172"/>
+      <c r="E2" s="172"/>
+      <c r="F2" s="172"/>
+    </row>
+    <row r="3" spans="1:9" ht="18.649999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B3" s="133"/>
       <c r="C3" s="50"/>
       <c r="D3" s="62"/>
       <c r="E3" s="62"/>
       <c r="F3" s="62"/>
     </row>
-    <row r="4" spans="1:9" ht="18.600000000000001" customHeight="1">
-      <c r="A4" s="183" t="s">
+    <row r="4" spans="1:9" ht="18.649999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="181" t="s">
         <v>375</v>
       </c>
-      <c r="B4" s="183"/>
-      <c r="C4" s="183"/>
-      <c r="D4" s="183"/>
-      <c r="E4" s="183"/>
-      <c r="F4" s="183"/>
-      <c r="G4" s="183"/>
-      <c r="H4" s="183"/>
+      <c r="B4" s="181"/>
+      <c r="C4" s="181"/>
+      <c r="D4" s="181"/>
+      <c r="E4" s="181"/>
+      <c r="F4" s="181"/>
+      <c r="G4" s="181"/>
+      <c r="H4" s="181"/>
       <c r="I4" s="127"/>
     </row>
-    <row r="5" spans="1:9" ht="33.6" customHeight="1">
-      <c r="A5" s="187" t="s">
+    <row r="5" spans="1:9" ht="33.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="185" t="s">
         <v>376</v>
       </c>
-      <c r="B5" s="188"/>
-      <c r="C5" s="188"/>
-      <c r="D5" s="188"/>
-      <c r="E5" s="188"/>
-      <c r="F5" s="188"/>
-      <c r="G5" s="188"/>
-      <c r="H5" s="188"/>
-    </row>
-    <row r="6" spans="1:9" ht="30.95">
+      <c r="B5" s="186"/>
+      <c r="C5" s="186"/>
+      <c r="D5" s="186"/>
+      <c r="E5" s="186"/>
+      <c r="F5" s="186"/>
+      <c r="G5" s="186"/>
+      <c r="H5" s="186"/>
+    </row>
+    <row r="6" spans="1:9" ht="31" x14ac:dyDescent="0.35">
       <c r="A6" s="28" t="s">
         <v>293</v>
       </c>
@@ -14998,7 +14981,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="7" spans="1:9" s="35" customFormat="1" ht="57.95">
+    <row r="7" spans="1:9" s="35" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A7" s="6" t="s">
         <v>377</v>
       </c>
@@ -15027,7 +15010,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="8" spans="1:9" s="35" customFormat="1">
+    <row r="8" spans="1:9" s="35" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A8" s="6" t="s">
         <v>384</v>
       </c>
@@ -15054,7 +15037,7 @@
       </c>
       <c r="I8" s="33"/>
     </row>
-    <row r="9" spans="1:9" s="35" customFormat="1" ht="43.5">
+    <row r="9" spans="1:9" s="35" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A9" s="6" t="s">
         <v>388</v>
       </c>
@@ -15081,7 +15064,7 @@
       </c>
       <c r="I9" s="33"/>
     </row>
-    <row r="10" spans="1:9" s="35" customFormat="1" ht="57.95">
+    <row r="10" spans="1:9" s="35" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A10" s="6" t="s">
         <v>393</v>
       </c>
@@ -15106,7 +15089,7 @@
       </c>
       <c r="I10" s="33"/>
     </row>
-    <row r="11" spans="1:9" s="35" customFormat="1" ht="29.1">
+    <row r="11" spans="1:9" s="35" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A11" s="6" t="s">
         <v>396</v>
       </c>
@@ -15133,7 +15116,7 @@
       </c>
       <c r="I11" s="33"/>
     </row>
-    <row r="12" spans="1:9" s="35" customFormat="1" ht="144.94999999999999">
+    <row r="12" spans="1:9" s="35" customFormat="1" ht="145" x14ac:dyDescent="0.35">
       <c r="A12" s="6" t="s">
         <v>399</v>
       </c>
@@ -15160,7 +15143,7 @@
       </c>
       <c r="I12" s="33"/>
     </row>
-    <row r="13" spans="1:9" s="35" customFormat="1">
+    <row r="13" spans="1:9" s="35" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A13" s="6" t="s">
         <v>403</v>
       </c>
@@ -15185,7 +15168,7 @@
       </c>
       <c r="I13" s="33"/>
     </row>
-    <row r="14" spans="1:9" s="35" customFormat="1" ht="29.1">
+    <row r="14" spans="1:9" s="35" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A14" s="6" t="s">
         <v>406</v>
       </c>
@@ -15210,7 +15193,7 @@
       </c>
       <c r="I14" s="33"/>
     </row>
-    <row r="15" spans="1:9" s="35" customFormat="1">
+    <row r="15" spans="1:9" s="35" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A15" s="6" t="s">
         <v>409</v>
       </c>
@@ -15235,7 +15218,7 @@
       </c>
       <c r="I15" s="33"/>
     </row>
-    <row r="16" spans="1:9" s="35" customFormat="1">
+    <row r="16" spans="1:9" s="35" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A16" s="6" t="s">
         <v>411</v>
       </c>
@@ -15260,7 +15243,7 @@
       </c>
       <c r="I16" s="33"/>
     </row>
-    <row r="17" spans="1:9" s="35" customFormat="1">
+    <row r="17" spans="1:9" s="35" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A17" s="6" t="s">
         <v>414</v>
       </c>
@@ -15285,7 +15268,7 @@
       </c>
       <c r="I17" s="33"/>
     </row>
-    <row r="18" spans="1:9" s="35" customFormat="1" ht="29.1">
+    <row r="18" spans="1:9" s="35" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A18" s="6" t="s">
         <v>417</v>
       </c>
@@ -15310,7 +15293,7 @@
       </c>
       <c r="I18" s="33"/>
     </row>
-    <row r="19" spans="1:9" s="35" customFormat="1">
+    <row r="19" spans="1:9" s="35" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A19" s="6" t="s">
         <v>420</v>
       </c>
@@ -15335,7 +15318,7 @@
       </c>
       <c r="I19" s="33"/>
     </row>
-    <row r="20" spans="1:9" s="35" customFormat="1">
+    <row r="20" spans="1:9" s="35" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A20" s="6" t="s">
         <v>422</v>
       </c>
@@ -15360,7 +15343,7 @@
       </c>
       <c r="I20" s="33"/>
     </row>
-    <row r="21" spans="1:9" s="35" customFormat="1">
+    <row r="21" spans="1:9" s="35" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A21" s="6" t="s">
         <v>425</v>
       </c>
@@ -15385,7 +15368,7 @@
       </c>
       <c r="I21" s="33"/>
     </row>
-    <row r="22" spans="1:9" s="35" customFormat="1">
+    <row r="22" spans="1:9" s="35" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A22" s="6" t="s">
         <v>428</v>
       </c>
@@ -15410,7 +15393,7 @@
       </c>
       <c r="I22" s="33"/>
     </row>
-    <row r="23" spans="1:9" s="35" customFormat="1">
+    <row r="23" spans="1:9" s="35" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A23" s="6" t="s">
         <v>430</v>
       </c>
@@ -15435,7 +15418,7 @@
       </c>
       <c r="I23" s="33"/>
     </row>
-    <row r="24" spans="1:9" s="35" customFormat="1" ht="29.1">
+    <row r="24" spans="1:9" s="35" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A24" s="6" t="s">
         <v>432</v>
       </c>
@@ -15460,7 +15443,7 @@
       </c>
       <c r="I24" s="33"/>
     </row>
-    <row r="25" spans="1:9" s="35" customFormat="1">
+    <row r="25" spans="1:9" s="35" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A25" s="6" t="s">
         <v>435</v>
       </c>
@@ -15485,7 +15468,7 @@
       </c>
       <c r="I25" s="33"/>
     </row>
-    <row r="26" spans="1:9" s="35" customFormat="1">
+    <row r="26" spans="1:9" s="35" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A26" s="6" t="s">
         <v>437</v>
       </c>
@@ -15510,7 +15493,7 @@
       </c>
       <c r="I26" s="33"/>
     </row>
-    <row r="27" spans="1:9" s="35" customFormat="1">
+    <row r="27" spans="1:9" s="35" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A27" s="6" t="s">
         <v>440</v>
       </c>
@@ -15535,7 +15518,7 @@
       </c>
       <c r="I27" s="33"/>
     </row>
-    <row r="28" spans="1:9" s="35" customFormat="1">
+    <row r="28" spans="1:9" s="35" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A28" s="6" t="s">
         <v>442</v>
       </c>
@@ -15560,7 +15543,7 @@
       </c>
       <c r="I28" s="33"/>
     </row>
-    <row r="29" spans="1:9" s="35" customFormat="1">
+    <row r="29" spans="1:9" s="35" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A29" s="6" t="s">
         <v>445</v>
       </c>
@@ -15585,7 +15568,7 @@
       </c>
       <c r="I29" s="33"/>
     </row>
-    <row r="30" spans="1:9" s="35" customFormat="1">
+    <row r="30" spans="1:9" s="35" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A30" s="6" t="s">
         <v>447</v>
       </c>
@@ -15610,7 +15593,7 @@
       </c>
       <c r="I30" s="33"/>
     </row>
-    <row r="31" spans="1:9" s="35" customFormat="1">
+    <row r="31" spans="1:9" s="35" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A31" s="6" t="s">
         <v>450</v>
       </c>
@@ -15635,7 +15618,7 @@
       </c>
       <c r="I31" s="33"/>
     </row>
-    <row r="32" spans="1:9" s="35" customFormat="1">
+    <row r="32" spans="1:9" s="35" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A32" s="6" t="s">
         <v>452</v>
       </c>
@@ -15660,7 +15643,7 @@
       </c>
       <c r="I32" s="33"/>
     </row>
-    <row r="33" spans="1:9" s="35" customFormat="1">
+    <row r="33" spans="1:9" s="35" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A33" s="6" t="s">
         <v>455</v>
       </c>
@@ -15685,14 +15668,14 @@
       </c>
       <c r="I33" s="33"/>
     </row>
-    <row r="34" spans="1:9">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
       <c r="C34" s="1"/>
     </row>
-    <row r="35" spans="1:9" ht="15">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B35" s="115"/>
       <c r="C35" s="1"/>
     </row>
-    <row r="42" spans="1:9">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.35">
       <c r="C42" s="3"/>
     </row>
   </sheetData>
@@ -15727,40 +15710,40 @@
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
   <dimension ref="A1:G9"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="17.85546875" style="35" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="68.85546875" style="35" customWidth="1"/>
-    <col min="3" max="3" width="21.140625" style="35" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="21.42578125" style="35" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="17.42578125" style="35" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="25.85546875" style="35" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.5703125" style="35" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="8.85546875" style="35"/>
+    <col min="1" max="1" width="17.81640625" style="35" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="68.81640625" style="35" customWidth="1"/>
+    <col min="3" max="3" width="21.1796875" style="35" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="21.453125" style="35" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="17.453125" style="35" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="25.81640625" style="35" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.54296875" style="35" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="8.81640625" style="35"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="23.45">
+    <row r="1" spans="1:7" ht="23.5" x14ac:dyDescent="0.35">
       <c r="A1" s="37"/>
     </row>
-    <row r="2" spans="1:7" ht="41.1" customHeight="1">
-      <c r="A2" s="184" t="s">
+    <row r="2" spans="1:7" ht="41.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="182" t="s">
         <v>457</v>
       </c>
-      <c r="B2" s="184"/>
-      <c r="C2" s="172"/>
-      <c r="D2" s="172"/>
-      <c r="E2" s="172"/>
-    </row>
-    <row r="3" spans="1:7" ht="41.1" customHeight="1">
+      <c r="B2" s="182"/>
+      <c r="C2" s="173"/>
+      <c r="D2" s="173"/>
+      <c r="E2" s="173"/>
+    </row>
+    <row r="3" spans="1:7" ht="41.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="49"/>
       <c r="B3" s="49"/>
-      <c r="C3" s="191"/>
-      <c r="D3" s="192"/>
-      <c r="E3" s="193"/>
+      <c r="C3" s="189"/>
+      <c r="D3" s="190"/>
+      <c r="E3" s="191"/>
       <c r="F3" s="101"/>
       <c r="G3"/>
     </row>
-    <row r="4" spans="1:7" ht="15.6">
+    <row r="4" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A4" s="34" t="s">
         <v>230</v>
       </c>
@@ -15783,7 +15766,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" s="6" t="s">
         <v>182</v>
       </c>
@@ -15806,7 +15789,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="29.1">
+    <row r="6" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A6" s="6" t="s">
         <v>12</v>
       </c>
@@ -15829,7 +15812,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="29.1">
+    <row r="7" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A7" s="6" t="s">
         <v>238</v>
       </c>
@@ -15852,7 +15835,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="101.45">
+    <row r="8" spans="1:7" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A8" s="8" t="s">
         <v>466</v>
       </c>
@@ -15875,7 +15858,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="87">
+    <row r="9" spans="1:7" ht="87" x14ac:dyDescent="0.35">
       <c r="A9" s="6" t="s">
         <v>26</v>
       </c>
@@ -15924,79 +15907,79 @@
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
   <dimension ref="A1:AF14"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="21.28515625" customWidth="1"/>
-    <col min="4" max="4" width="24.42578125" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="24.5703125" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="21.42578125" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="30.42578125" style="114" customWidth="1"/>
-    <col min="8" max="8" width="17.140625" style="114" customWidth="1"/>
-    <col min="10" max="10" width="63.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.26953125" customWidth="1"/>
+    <col min="4" max="4" width="24.453125" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="24.54296875" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="21.453125" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="30.453125" style="114" customWidth="1"/>
+    <col min="8" max="8" width="17.1796875" style="114" customWidth="1"/>
+    <col min="10" max="10" width="63.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" ht="23.45">
+    <row r="1" spans="1:32" ht="23.5" x14ac:dyDescent="0.55000000000000004">
       <c r="B1" s="30"/>
     </row>
-    <row r="2" spans="1:32">
-      <c r="B2" s="184" t="s">
+    <row r="2" spans="1:32" x14ac:dyDescent="0.35">
+      <c r="B2" s="182" t="s">
         <v>470</v>
       </c>
-      <c r="C2" s="184"/>
-      <c r="D2" s="171"/>
-      <c r="E2" s="171"/>
-      <c r="F2" s="171"/>
-    </row>
-    <row r="3" spans="1:32">
+      <c r="C2" s="182"/>
+      <c r="D2" s="172"/>
+      <c r="E2" s="172"/>
+      <c r="F2" s="172"/>
+    </row>
+    <row r="3" spans="1:32" x14ac:dyDescent="0.35">
       <c r="B3" s="49"/>
       <c r="C3" s="49"/>
       <c r="D3" s="108"/>
       <c r="E3" s="109"/>
       <c r="F3" s="110"/>
     </row>
-    <row r="4" spans="1:32">
+    <row r="4" spans="1:32" x14ac:dyDescent="0.35">
       <c r="B4" s="126"/>
       <c r="C4" s="126"/>
       <c r="D4" s="134"/>
       <c r="E4" s="135"/>
       <c r="F4" s="136"/>
     </row>
-    <row r="5" spans="1:32">
-      <c r="A5" s="183" t="s">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.35">
+      <c r="A5" s="181" t="s">
         <v>471</v>
       </c>
-      <c r="B5" s="183"/>
-      <c r="C5" s="183"/>
-      <c r="D5" s="183"/>
-      <c r="E5" s="183"/>
-      <c r="F5" s="183"/>
-      <c r="G5" s="183"/>
-      <c r="H5" s="183"/>
-    </row>
-    <row r="6" spans="1:32" ht="41.45" customHeight="1">
-      <c r="A6" s="188" t="s">
+      <c r="B5" s="181"/>
+      <c r="C5" s="181"/>
+      <c r="D5" s="181"/>
+      <c r="E5" s="181"/>
+      <c r="F5" s="181"/>
+      <c r="G5" s="181"/>
+      <c r="H5" s="181"/>
+    </row>
+    <row r="6" spans="1:32" ht="41.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="186" t="s">
         <v>472</v>
       </c>
-      <c r="B6" s="188"/>
-      <c r="C6" s="188"/>
-      <c r="D6" s="188"/>
-      <c r="E6" s="188"/>
-      <c r="F6" s="188"/>
-      <c r="G6" s="188"/>
-      <c r="H6" s="188"/>
+      <c r="B6" s="186"/>
+      <c r="C6" s="186"/>
+      <c r="D6" s="186"/>
+      <c r="E6" s="186"/>
+      <c r="F6" s="186"/>
+      <c r="G6" s="186"/>
+      <c r="H6" s="186"/>
       <c r="AA6" t="s">
         <v>473</v>
       </c>
-      <c r="AB6" s="194" t="s">
+      <c r="AB6" s="192" t="s">
         <v>474</v>
       </c>
-      <c r="AC6" s="194"/>
-      <c r="AD6" s="194"/>
-      <c r="AE6" s="194"/>
-      <c r="AF6" s="194"/>
-    </row>
-    <row r="7" spans="1:32" s="64" customFormat="1" ht="29.45" customHeight="1">
+      <c r="AC6" s="192"/>
+      <c r="AD6" s="192"/>
+      <c r="AE6" s="192"/>
+      <c r="AF6" s="192"/>
+    </row>
+    <row r="7" spans="1:32" s="64" customFormat="1" ht="29.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="28" t="s">
         <v>293</v>
       </c>
@@ -16043,7 +16026,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="8" spans="1:32" ht="43.5">
+    <row r="8" spans="1:32" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A8" s="6" t="s">
         <v>481</v>
       </c>
@@ -16070,7 +16053,7 @@
       </c>
       <c r="I8" s="3"/>
     </row>
-    <row r="9" spans="1:32" ht="29.1">
+    <row r="9" spans="1:32" ht="29" x14ac:dyDescent="0.35">
       <c r="A9" s="6" t="s">
         <v>485</v>
       </c>
@@ -16097,7 +16080,7 @@
       </c>
       <c r="I9" s="3"/>
     </row>
-    <row r="10" spans="1:32" ht="43.5">
+    <row r="10" spans="1:32" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A10" s="6" t="s">
         <v>489</v>
       </c>
@@ -16127,7 +16110,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="11" spans="1:32" ht="72.599999999999994">
+    <row r="11" spans="1:32" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A11" s="6" t="s">
         <v>493</v>
       </c>
@@ -16154,13 +16137,13 @@
       </c>
       <c r="I11" s="3"/>
     </row>
-    <row r="12" spans="1:32">
+    <row r="12" spans="1:32" x14ac:dyDescent="0.35">
       <c r="C12" s="1"/>
     </row>
-    <row r="13" spans="1:32">
+    <row r="13" spans="1:32" x14ac:dyDescent="0.35">
       <c r="C13" s="1"/>
     </row>
-    <row r="14" spans="1:32">
+    <row r="14" spans="1:32" x14ac:dyDescent="0.35">
       <c r="C14" s="1"/>
     </row>
   </sheetData>
@@ -16184,21 +16167,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E43A70CC58D90D42810A5FB4E341896E" ma:contentTypeVersion="3" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="cdcdf9498ba422245be6c23454f89730">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="edcbf321-57e4-4ccd-8840-ac477e9a426a" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="186c8377d1779e329dbc41d4412f5cb8" ns2:_="">
     <xsd:import namespace="edcbf321-57e4-4ccd-8840-ac477e9a426a"/>
@@ -16336,14 +16304,52 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FF3AF32B-3389-4459-9892-0CB366BDC7B3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EAB37A65-CDD2-42D1-B877-E15427ECEA2A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="edcbf321-57e4-4ccd-8840-ac477e9a426a"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE8FBFAC-E23D-4BB4-8CBF-896F42440E38}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE8FBFAC-E23D-4BB4-8CBF-896F42440E38}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EAB37A65-CDD2-42D1-B877-E15427ECEA2A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FF3AF32B-3389-4459-9892-0CB366BDC7B3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/TCPL Rulesets - GL1 (1).xlsx
+++ b/TCPL Rulesets - GL1 (1).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SEM-8\Data Rules Set Check\Data_rulesets_check\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9312E81D-AAD5-4E34-8FC0-047236D466A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A1D9F45-8178-426E-B307-EEB069DA8D87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="906" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="906" firstSheet="2" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data Availability backup" sheetId="89" state="hidden" r:id="rId1"/>
@@ -3548,6 +3548,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3556,9 +3559,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -5810,43 +5810,43 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B2" s="173" t="s">
+      <c r="B2" s="170" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="170" t="s">
+      <c r="C2" s="171" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="173" t="s">
+      <c r="D2" s="170" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="170" t="s">
+      <c r="E2" s="171" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="170" t="s">
+      <c r="F2" s="171" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="170" t="s">
+      <c r="G2" s="171" t="s">
         <v>5</v>
       </c>
-      <c r="H2" s="170" t="s">
+      <c r="H2" s="171" t="s">
         <v>6</v>
       </c>
       <c r="I2" s="77"/>
-      <c r="J2" s="172" t="s">
+      <c r="J2" s="173" t="s">
         <v>7</v>
       </c>
-      <c r="K2" s="172"/>
-      <c r="L2" s="172"/>
-      <c r="M2" s="172"/>
+      <c r="K2" s="173"/>
+      <c r="L2" s="173"/>
+      <c r="M2" s="173"/>
     </row>
     <row r="3" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B3" s="173"/>
-      <c r="C3" s="171"/>
-      <c r="D3" s="173"/>
-      <c r="E3" s="171"/>
-      <c r="F3" s="171"/>
-      <c r="G3" s="171"/>
-      <c r="H3" s="171"/>
+      <c r="B3" s="170"/>
+      <c r="C3" s="172"/>
+      <c r="D3" s="170"/>
+      <c r="E3" s="172"/>
+      <c r="F3" s="172"/>
+      <c r="G3" s="172"/>
+      <c r="H3" s="172"/>
       <c r="I3" s="78"/>
       <c r="J3" s="4" t="s">
         <v>8</v>
@@ -7143,11 +7143,12 @@
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="B26:B31"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="B32:B49"/>
+    <mergeCell ref="C32:C49"/>
+    <mergeCell ref="B50:B61"/>
+    <mergeCell ref="C50:C61"/>
+    <mergeCell ref="B62:B67"/>
+    <mergeCell ref="C62:C67"/>
     <mergeCell ref="H2:H3"/>
     <mergeCell ref="J2:M2"/>
     <mergeCell ref="B4:B11"/>
@@ -7155,12 +7156,11 @@
     <mergeCell ref="B24:B25"/>
     <mergeCell ref="F2:F3"/>
     <mergeCell ref="G2:G3"/>
-    <mergeCell ref="B32:B49"/>
-    <mergeCell ref="C32:C49"/>
-    <mergeCell ref="B50:B61"/>
-    <mergeCell ref="C50:C61"/>
-    <mergeCell ref="B62:B67"/>
-    <mergeCell ref="C62:C67"/>
+    <mergeCell ref="B26:B31"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="E2:E3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -7196,9 +7196,9 @@
         <v>497</v>
       </c>
       <c r="C2" s="194"/>
-      <c r="D2" s="173"/>
-      <c r="E2" s="173"/>
-      <c r="F2" s="173"/>
+      <c r="D2" s="170"/>
+      <c r="E2" s="170"/>
+      <c r="F2" s="170"/>
     </row>
     <row r="3" spans="1:9" ht="26.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B3" s="51"/>
@@ -7639,7 +7639,7 @@
       <selection activeCell="H4" sqref="H4:J11"/>
       <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
       <pageSetup orientation="portrait" r:id="rId1"/>
-      <autoFilter ref="A2:O16" xr:uid="{A32CD63E-D77B-49C0-A296-A4378B8086AC}">
+      <autoFilter ref="A2:O16" xr:uid="{8095BEDC-A695-4DDC-A442-DFE8BA62A908}">
         <filterColumn colId="11">
           <filters>
             <filter val="No"/>
@@ -7697,9 +7697,9 @@
         <v>549</v>
       </c>
       <c r="C2" s="197"/>
-      <c r="D2" s="172"/>
-      <c r="E2" s="172"/>
-      <c r="F2" s="172"/>
+      <c r="D2" s="173"/>
+      <c r="E2" s="173"/>
+      <c r="F2" s="173"/>
     </row>
     <row r="3" spans="1:9" ht="39.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B3" s="49"/>
@@ -7934,9 +7934,9 @@
         <v>549</v>
       </c>
       <c r="C2" s="197"/>
-      <c r="D2" s="172"/>
-      <c r="E2" s="172"/>
-      <c r="F2" s="172"/>
+      <c r="D2" s="173"/>
+      <c r="E2" s="173"/>
+      <c r="F2" s="173"/>
     </row>
     <row r="3" spans="1:9" ht="39.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B3" s="49"/>
@@ -8162,8 +8162,8 @@
         <v>576</v>
       </c>
       <c r="C2" s="205"/>
-      <c r="D2" s="172"/>
-      <c r="E2" s="172"/>
+      <c r="D2" s="173"/>
+      <c r="E2" s="173"/>
     </row>
     <row r="3" spans="1:8" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B3" s="150"/>
@@ -8178,15 +8178,15 @@
       <c r="E4" s="62"/>
     </row>
     <row r="5" spans="1:8" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="173" t="s">
+      <c r="A5" s="170" t="s">
         <v>577</v>
       </c>
-      <c r="B5" s="173"/>
-      <c r="C5" s="173"/>
-      <c r="D5" s="173"/>
-      <c r="E5" s="173"/>
-      <c r="F5" s="173"/>
-      <c r="G5" s="173"/>
+      <c r="B5" s="170"/>
+      <c r="C5" s="170"/>
+      <c r="D5" s="170"/>
+      <c r="E5" s="170"/>
+      <c r="F5" s="170"/>
+      <c r="G5" s="170"/>
       <c r="H5" s="155"/>
     </row>
     <row r="6" spans="1:8" ht="29.15" customHeight="1" x14ac:dyDescent="0.35">
@@ -8872,9 +8872,9 @@
         <v>654</v>
       </c>
       <c r="B2" s="206"/>
-      <c r="C2" s="172"/>
-      <c r="D2" s="172"/>
-      <c r="E2" s="172"/>
+      <c r="C2" s="173"/>
+      <c r="D2" s="173"/>
+      <c r="E2" s="173"/>
     </row>
     <row r="3" spans="1:7" ht="45.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="27"/>
@@ -8989,9 +8989,9 @@
         <v>658</v>
       </c>
       <c r="B2" s="182"/>
-      <c r="C2" s="172"/>
-      <c r="D2" s="172"/>
-      <c r="E2" s="172"/>
+      <c r="C2" s="173"/>
+      <c r="D2" s="173"/>
+      <c r="E2" s="173"/>
     </row>
     <row r="3" spans="1:7" ht="46.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="49"/>
@@ -14602,9 +14602,9 @@
         <v>338</v>
       </c>
       <c r="C2" s="182"/>
-      <c r="D2" s="172"/>
-      <c r="E2" s="172"/>
-      <c r="F2" s="172"/>
+      <c r="D2" s="173"/>
+      <c r="E2" s="173"/>
+      <c r="F2" s="173"/>
     </row>
     <row r="3" spans="1:12" ht="56.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B3" s="126"/>
@@ -14868,7 +14868,7 @@
       <selection sqref="A1:K1"/>
       <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
       <pageSetup orientation="portrait" r:id="rId1"/>
-      <autoFilter ref="A2:P11" xr:uid="{EB255A04-2606-4BD1-9866-2FCFFA079BE9}"/>
+      <autoFilter ref="A2:P11" xr:uid="{31D135D1-19CC-4FAC-B376-2E81581D0D4E}"/>
     </customSheetView>
   </customSheetViews>
   <mergeCells count="5">
@@ -14916,9 +14916,9 @@
         <v>374</v>
       </c>
       <c r="C2" s="188"/>
-      <c r="D2" s="172"/>
-      <c r="E2" s="172"/>
-      <c r="F2" s="172"/>
+      <c r="D2" s="173"/>
+      <c r="E2" s="173"/>
+      <c r="F2" s="173"/>
     </row>
     <row r="3" spans="1:9" ht="18.649999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B3" s="133"/>
@@ -15730,9 +15730,9 @@
         <v>457</v>
       </c>
       <c r="B2" s="182"/>
-      <c r="C2" s="173"/>
-      <c r="D2" s="173"/>
-      <c r="E2" s="173"/>
+      <c r="C2" s="170"/>
+      <c r="D2" s="170"/>
+      <c r="E2" s="170"/>
     </row>
     <row r="3" spans="1:7" ht="41.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="49"/>
@@ -15927,9 +15927,9 @@
         <v>470</v>
       </c>
       <c r="C2" s="182"/>
-      <c r="D2" s="172"/>
-      <c r="E2" s="172"/>
-      <c r="F2" s="172"/>
+      <c r="D2" s="173"/>
+      <c r="E2" s="173"/>
+      <c r="F2" s="173"/>
     </row>
     <row r="3" spans="1:32" x14ac:dyDescent="0.35">
       <c r="B3" s="49"/>
@@ -16167,6 +16167,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E43A70CC58D90D42810A5FB4E341896E" ma:contentTypeVersion="3" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="cdcdf9498ba422245be6c23454f89730">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="edcbf321-57e4-4ccd-8840-ac477e9a426a" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="186c8377d1779e329dbc41d4412f5cb8" ns2:_="">
     <xsd:import namespace="edcbf321-57e4-4ccd-8840-ac477e9a426a"/>
@@ -16304,22 +16319,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FF3AF32B-3389-4459-9892-0CB366BDC7B3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE8FBFAC-E23D-4BB4-8CBF-896F42440E38}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EAB37A65-CDD2-42D1-B877-E15427ECEA2A}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -16335,21 +16352,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE8FBFAC-E23D-4BB4-8CBF-896F42440E38}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FF3AF32B-3389-4459-9892-0CB366BDC7B3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/TCPL Rulesets - GL1 (1).xlsx
+++ b/TCPL Rulesets - GL1 (1).xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SEM-8\Data Rules Set Check\Data_rulesets_check\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SW526XH\Downloads\Data Quality Check\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A1D9F45-8178-426E-B307-EEB069DA8D87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{954E4218-E8A8-4269-9539-16B5C55279DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="906" firstSheet="2" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" tabRatio="906" firstSheet="2" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data Availability backup" sheetId="89" state="hidden" r:id="rId1"/>
@@ -75,21 +75,21 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata">
   <metadataTypes count="1">
     <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
   </metadataTypes>
   <futureMetadata name="XLRICHVALUE" count="2">
     <bk>
       <extLst>
-        <ext xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
           <xlrd:rvb i="0"/>
         </ext>
       </extLst>
     </bk>
     <bk>
       <extLst>
-        <ext xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
           <xlrd:rvb i="1"/>
         </ext>
       </extLst>
@@ -1280,10 +1280,6 @@
   </si>
   <si>
     <t>CompanyCode</t>
-  </si>
-  <si>
-    <t>1. Field should be 1001 / 1006 / 1009
-2.Field should not be blank</t>
   </si>
   <si>
     <t>Production Plant</t>
@@ -2535,6 +2531,9 @@
   </si>
   <si>
     <t>DisplayValue</t>
+  </si>
+  <si>
+    <t>1. Field should be 1001 / 1006 / 1009 2.Field should not be blank</t>
   </si>
 </sst>
 </file>
@@ -5498,9 +5497,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -5538,7 +5537,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -5644,7 +5643,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -5786,7 +5785,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -7193,7 +7192,7 @@
     </row>
     <row r="2" spans="1:9" ht="26.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B2" s="193" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="C2" s="194"/>
       <c r="D2" s="170"/>
@@ -7216,7 +7215,7 @@
     </row>
     <row r="5" spans="1:9" ht="26.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="181" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B5" s="181"/>
       <c r="C5" s="181"/>
@@ -7228,7 +7227,7 @@
     </row>
     <row r="6" spans="1:9" ht="32.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="195" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B6" s="195"/>
       <c r="C6" s="195"/>
@@ -7253,7 +7252,7 @@
         <v>295</v>
       </c>
       <c r="E7" s="47" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="F7" s="47" t="s">
         <v>234</v>
@@ -7270,22 +7269,22 @@
     </row>
     <row r="8" spans="1:9" ht="29" x14ac:dyDescent="0.35">
       <c r="A8" s="6" t="s">
+        <v>500</v>
+      </c>
+      <c r="B8" s="6" t="s">
         <v>501</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="C8" s="8" t="s">
         <v>502</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>503</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>235</v>
       </c>
       <c r="E8" s="106" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="F8" s="106" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="G8" s="26" t="s">
         <v>312</v>
@@ -7297,22 +7296,22 @@
     </row>
     <row r="9" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A9" s="6" t="s">
+        <v>503</v>
+      </c>
+      <c r="B9" s="120" t="s">
         <v>504</v>
       </c>
-      <c r="B9" s="120" t="s">
+      <c r="C9" s="8" t="s">
         <v>505</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>506</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>235</v>
       </c>
       <c r="E9" s="106" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="F9" s="106" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="G9" s="26" t="s">
         <v>312</v>
@@ -7324,25 +7323,25 @@
     </row>
     <row r="10" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A10" s="6" t="s">
+        <v>506</v>
+      </c>
+      <c r="B10" s="120" t="s">
         <v>507</v>
       </c>
-      <c r="B10" s="120" t="s">
-        <v>508</v>
-      </c>
       <c r="C10" s="8" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>235</v>
       </c>
       <c r="E10" s="106" t="s">
+        <v>462</v>
+      </c>
+      <c r="F10" s="106" t="s">
         <v>463</v>
       </c>
-      <c r="F10" s="106" t="s">
-        <v>464</v>
-      </c>
       <c r="G10" s="24" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H10" s="24" t="s">
         <v>308</v>
@@ -7351,20 +7350,20 @@
     </row>
     <row r="11" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A11" s="6" t="s">
+        <v>509</v>
+      </c>
+      <c r="B11" s="120" t="s">
         <v>510</v>
       </c>
-      <c r="B11" s="120" t="s">
-        <v>511</v>
-      </c>
       <c r="C11" s="8" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="D11" s="6"/>
       <c r="E11" s="106" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F11" s="106" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="G11" s="26" t="s">
         <v>312</v>
@@ -7376,23 +7375,23 @@
     </row>
     <row r="12" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A12" s="6" t="s">
+        <v>512</v>
+      </c>
+      <c r="B12" s="120" t="s">
         <v>513</v>
       </c>
-      <c r="B12" s="120" t="s">
+      <c r="C12" s="6" t="s">
         <v>514</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>515</v>
       </c>
       <c r="D12" s="6"/>
       <c r="E12" s="106" t="s">
+        <v>458</v>
+      </c>
+      <c r="F12" s="106" t="s">
         <v>459</v>
       </c>
-      <c r="F12" s="106" t="s">
-        <v>460</v>
-      </c>
       <c r="G12" s="145" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H12" s="24" t="s">
         <v>308</v>
@@ -7401,20 +7400,20 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A13" s="6" t="s">
+        <v>516</v>
+      </c>
+      <c r="B13" s="6" t="s">
         <v>517</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="C13" s="8" t="s">
         <v>518</v>
-      </c>
-      <c r="C13" s="8" t="s">
-        <v>519</v>
       </c>
       <c r="D13" s="6"/>
       <c r="E13" s="106" t="s">
+        <v>519</v>
+      </c>
+      <c r="F13" s="106" t="s">
         <v>520</v>
-      </c>
-      <c r="F13" s="106" t="s">
-        <v>521</v>
       </c>
       <c r="G13" s="26" t="s">
         <v>312</v>
@@ -7426,13 +7425,13 @@
     </row>
     <row r="14" spans="1:9" ht="145" x14ac:dyDescent="0.35">
       <c r="A14" s="6" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="B14" s="8" t="s">
         <v>26</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="D14" s="6"/>
       <c r="E14" s="106" t="s">
@@ -7451,13 +7450,13 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A15" s="6" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B15" s="6" t="s">
         <v>58</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="D15" s="6"/>
       <c r="E15" s="106" t="s">
@@ -7476,23 +7475,23 @@
     </row>
     <row r="16" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A16" s="6" t="s">
+        <v>525</v>
+      </c>
+      <c r="B16" s="120" t="s">
         <v>526</v>
       </c>
-      <c r="B16" s="120" t="s">
+      <c r="C16" s="8" t="s">
         <v>527</v>
-      </c>
-      <c r="C16" s="8" t="s">
-        <v>528</v>
       </c>
       <c r="D16" s="6"/>
       <c r="E16" s="106" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="F16" s="16" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="G16" s="24" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="H16" s="24" t="s">
         <v>308</v>
@@ -7501,23 +7500,23 @@
     </row>
     <row r="17" spans="1:9" ht="29" x14ac:dyDescent="0.35">
       <c r="A17" s="6" t="s">
+        <v>529</v>
+      </c>
+      <c r="B17" s="120" t="s">
         <v>530</v>
       </c>
-      <c r="B17" s="120" t="s">
+      <c r="C17" s="8" t="s">
         <v>531</v>
-      </c>
-      <c r="C17" s="8" t="s">
-        <v>532</v>
       </c>
       <c r="D17" s="6"/>
       <c r="E17" s="106" t="s">
+        <v>462</v>
+      </c>
+      <c r="F17" s="16" t="s">
         <v>463</v>
       </c>
-      <c r="F17" s="16" t="s">
-        <v>464</v>
-      </c>
       <c r="G17" s="24" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H17" s="24" t="s">
         <v>308</v>
@@ -7526,20 +7525,20 @@
     </row>
     <row r="18" spans="1:9" ht="29" x14ac:dyDescent="0.35">
       <c r="A18" s="6" t="s">
+        <v>533</v>
+      </c>
+      <c r="B18" s="6" t="s">
         <v>534</v>
       </c>
-      <c r="B18" s="6" t="s">
+      <c r="C18" s="8" t="s">
         <v>535</v>
-      </c>
-      <c r="C18" s="8" t="s">
-        <v>536</v>
       </c>
       <c r="D18" s="6"/>
       <c r="E18" s="107" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="F18" s="16" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="G18" s="26" t="s">
         <v>312</v>
@@ -7551,20 +7550,20 @@
     </row>
     <row r="19" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A19" s="6" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="B19" s="6" t="s">
         <v>59</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="D19" s="6"/>
       <c r="E19" s="106" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="F19" s="16" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="G19" s="26" t="s">
         <v>312</v>
@@ -7576,20 +7575,20 @@
     </row>
     <row r="20" spans="1:9" ht="41.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="6" t="s">
+        <v>540</v>
+      </c>
+      <c r="B20" s="6" t="s">
         <v>541</v>
       </c>
-      <c r="B20" s="6" t="s">
+      <c r="C20" s="8" t="s">
         <v>542</v>
-      </c>
-      <c r="C20" s="8" t="s">
-        <v>543</v>
       </c>
       <c r="D20" s="6"/>
       <c r="E20" s="106" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="F20" s="16" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="G20" s="26" t="s">
         <v>312</v>
@@ -7601,13 +7600,13 @@
     </row>
     <row r="21" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A21" s="6" t="s">
+        <v>544</v>
+      </c>
+      <c r="B21" s="120" t="s">
         <v>545</v>
       </c>
-      <c r="B21" s="120" t="s">
+      <c r="C21" s="8" t="s">
         <v>546</v>
-      </c>
-      <c r="C21" s="8" t="s">
-        <v>547</v>
       </c>
       <c r="D21" s="6"/>
       <c r="E21" s="106" t="s">
@@ -7629,7 +7628,7 @@
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B23" s="35" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="F23" s="61"/>
     </row>
@@ -7639,7 +7638,7 @@
       <selection activeCell="H4" sqref="H4:J11"/>
       <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
       <pageSetup orientation="portrait" r:id="rId1"/>
-      <autoFilter ref="A2:O16" xr:uid="{8095BEDC-A695-4DDC-A442-DFE8BA62A908}">
+      <autoFilter ref="A2:O16" xr:uid="{9C1F0F38-FB03-4A75-8325-9FA0BD6F4877}">
         <filterColumn colId="11">
           <filters>
             <filter val="No"/>
@@ -7694,7 +7693,7 @@
     </row>
     <row r="2" spans="1:9" ht="39.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B2" s="196" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="C2" s="197"/>
       <c r="D2" s="173"/>
@@ -7717,7 +7716,7 @@
     </row>
     <row r="5" spans="1:9" ht="39.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="198" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B5" s="199"/>
       <c r="C5" s="199"/>
@@ -7730,7 +7729,7 @@
     </row>
     <row r="6" spans="1:9" ht="39.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="201" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B6" s="202"/>
       <c r="C6" s="202"/>
@@ -7772,25 +7771,25 @@
     </row>
     <row r="8" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A8" s="6" t="s">
+        <v>551</v>
+      </c>
+      <c r="B8" s="8" t="s">
         <v>552</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="C8" s="8" t="s">
         <v>553</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>554</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>235</v>
       </c>
       <c r="E8" s="106" t="s">
+        <v>554</v>
+      </c>
+      <c r="F8" s="106" t="s">
         <v>555</v>
       </c>
-      <c r="F8" s="106" t="s">
-        <v>556</v>
-      </c>
       <c r="G8" s="24" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="H8" s="24" t="s">
         <v>308</v>
@@ -7799,25 +7798,25 @@
     </row>
     <row r="9" spans="1:9" ht="29" x14ac:dyDescent="0.35">
       <c r="A9" s="6" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="B9" s="8" t="s">
         <v>238</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>235</v>
       </c>
       <c r="E9" s="106" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="F9" s="106" t="s">
         <v>43</v>
       </c>
       <c r="G9" s="24" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H9" s="24" t="s">
         <v>308</v>
@@ -7826,25 +7825,25 @@
     </row>
     <row r="10" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A10" s="6" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B10" s="8" t="s">
         <v>182</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>235</v>
       </c>
       <c r="E10" s="106" t="s">
+        <v>560</v>
+      </c>
+      <c r="F10" s="106" t="s">
         <v>561</v>
       </c>
-      <c r="F10" s="106" t="s">
-        <v>562</v>
-      </c>
       <c r="G10" s="56" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H10" s="24" t="s">
         <v>308</v>
@@ -7853,25 +7852,25 @@
     </row>
     <row r="11" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A11" s="6" t="s">
+        <v>562</v>
+      </c>
+      <c r="B11" s="122" t="s">
         <v>563</v>
       </c>
-      <c r="B11" s="122" t="s">
+      <c r="C11" s="59" t="s">
         <v>564</v>
-      </c>
-      <c r="C11" s="59" t="s">
-        <v>565</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>235</v>
       </c>
       <c r="E11" s="106" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="F11" s="106" t="s">
+        <v>565</v>
+      </c>
+      <c r="G11" s="24" t="s">
         <v>566</v>
-      </c>
-      <c r="G11" s="24" t="s">
-        <v>567</v>
       </c>
       <c r="H11" s="24" t="s">
         <v>302</v>
@@ -7880,7 +7879,7 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B14" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
     </row>
   </sheetData>
@@ -7931,7 +7930,7 @@
     </row>
     <row r="2" spans="1:9" ht="39.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B2" s="196" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="C2" s="197"/>
       <c r="D2" s="173"/>
@@ -7954,7 +7953,7 @@
     </row>
     <row r="5" spans="1:9" ht="39.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="198" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="B5" s="199"/>
       <c r="C5" s="199"/>
@@ -7966,7 +7965,7 @@
     </row>
     <row r="6" spans="1:9" ht="39.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="186" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="B6" s="186"/>
       <c r="C6" s="186"/>
@@ -8007,25 +8006,25 @@
     </row>
     <row r="8" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A8" s="6" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="B8" s="8" t="s">
+        <v>552</v>
+      </c>
+      <c r="C8" s="8" t="s">
         <v>553</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>554</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>235</v>
       </c>
       <c r="E8" s="6" t="s">
+        <v>554</v>
+      </c>
+      <c r="F8" s="106" t="s">
         <v>555</v>
       </c>
-      <c r="F8" s="106" t="s">
-        <v>556</v>
-      </c>
       <c r="G8" s="24" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="H8" s="24" t="s">
         <v>308</v>
@@ -8034,25 +8033,25 @@
     </row>
     <row r="9" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A9" s="6" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="B9" s="8" t="s">
         <v>238</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>235</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="F9" s="106" t="s">
         <v>43</v>
       </c>
       <c r="G9" s="24" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H9" s="24" t="s">
         <v>308</v>
@@ -8061,25 +8060,25 @@
     </row>
     <row r="10" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A10" s="6" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="B10" s="8" t="s">
         <v>182</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>235</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="F10" s="106" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="G10" s="56" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H10" s="24" t="s">
         <v>308</v>
@@ -8088,25 +8087,25 @@
     </row>
     <row r="11" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A11" s="6" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="B11" s="122" t="s">
+        <v>563</v>
+      </c>
+      <c r="C11" s="59" t="s">
         <v>564</v>
-      </c>
-      <c r="C11" s="59" t="s">
-        <v>565</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>235</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="F11" s="106" t="s">
+        <v>565</v>
+      </c>
+      <c r="G11" s="24" t="s">
         <v>566</v>
-      </c>
-      <c r="G11" s="24" t="s">
-        <v>567</v>
       </c>
       <c r="H11" s="24" t="s">
         <v>302</v>
@@ -8159,7 +8158,7 @@
     </row>
     <row r="2" spans="1:8" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B2" s="204" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="C2" s="205"/>
       <c r="D2" s="173"/>
@@ -8179,7 +8178,7 @@
     </row>
     <row r="5" spans="1:8" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="170" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B5" s="170"/>
       <c r="C5" s="170"/>
@@ -8191,7 +8190,7 @@
     </row>
     <row r="6" spans="1:8" ht="29.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="169" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B6" s="169"/>
       <c r="C6" s="169"/>
@@ -8229,13 +8228,13 @@
     </row>
     <row r="8" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A8" s="6" t="s">
+        <v>578</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>552</v>
+      </c>
+      <c r="C8" s="6" t="s">
         <v>579</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>553</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>580</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>276</v>
@@ -8244,33 +8243,33 @@
         <v>82</v>
       </c>
       <c r="F8" s="24" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="G8" s="72" t="s">
         <v>302</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A9" s="6" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>240</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>243</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="F9" s="24" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="G9" s="72" t="s">
         <v>302</v>
@@ -8279,20 +8278,20 @@
     </row>
     <row r="10" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A10" s="6" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>74</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="6" t="s">
+        <v>586</v>
+      </c>
+      <c r="E10" s="6" t="s">
         <v>587</v>
       </c>
-      <c r="E10" s="6" t="s">
-        <v>588</v>
-      </c>
       <c r="F10" s="24" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="G10" s="72" t="s">
         <v>302</v>
@@ -8301,20 +8300,20 @@
     </row>
     <row r="11" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A11" s="6" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>75</v>
       </c>
       <c r="C11" s="6"/>
       <c r="D11" s="6" t="s">
+        <v>589</v>
+      </c>
+      <c r="E11" s="6" t="s">
         <v>590</v>
       </c>
-      <c r="E11" s="6" t="s">
-        <v>591</v>
-      </c>
       <c r="F11" s="24" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="G11" s="72" t="s">
         <v>302</v>
@@ -8323,22 +8322,22 @@
     </row>
     <row r="12" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A12" s="6" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B12" s="153" t="s">
         <v>76</v>
       </c>
       <c r="C12" s="153" t="s">
+        <v>592</v>
+      </c>
+      <c r="D12" s="6" t="s">
         <v>593</v>
       </c>
-      <c r="D12" s="6" t="s">
-        <v>594</v>
-      </c>
       <c r="E12" s="153" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="F12" s="24" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="G12" s="72" t="s">
         <v>302</v>
@@ -8347,22 +8346,22 @@
     </row>
     <row r="13" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A13" s="6" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="B13" s="153" t="s">
         <v>78</v>
       </c>
       <c r="C13" s="153" t="s">
+        <v>595</v>
+      </c>
+      <c r="D13" s="154" t="s">
         <v>596</v>
       </c>
-      <c r="D13" s="154" t="s">
+      <c r="E13" s="6" t="s">
         <v>597</v>
       </c>
-      <c r="E13" s="6" t="s">
-        <v>598</v>
-      </c>
       <c r="F13" s="24" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="G13" s="72" t="s">
         <v>302</v>
@@ -8371,22 +8370,22 @@
     </row>
     <row r="14" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A14" s="6" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>79</v>
       </c>
       <c r="C14" s="6" t="s">
+        <v>599</v>
+      </c>
+      <c r="D14" s="6" t="s">
         <v>600</v>
       </c>
-      <c r="D14" s="6" t="s">
+      <c r="E14" s="6" t="s">
         <v>601</v>
       </c>
-      <c r="E14" s="6" t="s">
-        <v>602</v>
-      </c>
       <c r="F14" s="24" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="G14" s="72" t="s">
         <v>302</v>
@@ -8395,22 +8394,22 @@
     </row>
     <row r="15" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A15" s="6" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="B15" s="6" t="s">
         <v>81</v>
       </c>
       <c r="C15" s="6" t="s">
+        <v>603</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>600</v>
+      </c>
+      <c r="E15" s="6" t="s">
         <v>604</v>
       </c>
-      <c r="D15" s="6" t="s">
-        <v>601</v>
-      </c>
-      <c r="E15" s="6" t="s">
-        <v>605</v>
-      </c>
       <c r="F15" s="24" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="G15" s="72" t="s">
         <v>302</v>
@@ -8419,22 +8418,22 @@
     </row>
     <row r="16" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A16" s="6" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>82</v>
       </c>
       <c r="C16" s="122" t="s">
+        <v>606</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>600</v>
+      </c>
+      <c r="E16" s="6" t="s">
         <v>607</v>
       </c>
-      <c r="D16" s="6" t="s">
-        <v>601</v>
-      </c>
-      <c r="E16" s="6" t="s">
-        <v>608</v>
-      </c>
       <c r="F16" s="24" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="G16" s="72" t="s">
         <v>302</v>
@@ -8443,22 +8442,22 @@
     </row>
     <row r="17" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A17" s="6" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="B17" s="6" t="s">
         <v>84</v>
       </c>
       <c r="C17" s="122" t="s">
+        <v>609</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>600</v>
+      </c>
+      <c r="E17" s="6" t="s">
         <v>610</v>
       </c>
-      <c r="D17" s="6" t="s">
-        <v>601</v>
-      </c>
-      <c r="E17" s="6" t="s">
-        <v>611</v>
-      </c>
       <c r="F17" s="24" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="G17" s="72" t="s">
         <v>302</v>
@@ -8467,20 +8466,20 @@
     </row>
     <row r="18" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A18" s="6" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>85</v>
       </c>
       <c r="C18" s="122"/>
       <c r="D18" s="6" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="E18" s="154" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="F18" s="24" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="G18" s="72" t="s">
         <v>302</v>
@@ -8489,20 +8488,20 @@
     </row>
     <row r="19" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A19" s="6" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="B19" s="6" t="s">
         <v>86</v>
       </c>
       <c r="C19" s="122"/>
       <c r="D19" s="6" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="E19" s="154" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="F19" s="24" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="G19" s="72" t="s">
         <v>302</v>
@@ -8511,22 +8510,22 @@
     </row>
     <row r="20" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A20" s="6" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>87</v>
       </c>
       <c r="C20" s="122" t="s">
+        <v>616</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>600</v>
+      </c>
+      <c r="E20" s="6" t="s">
         <v>617</v>
       </c>
-      <c r="D20" s="6" t="s">
-        <v>601</v>
-      </c>
-      <c r="E20" s="6" t="s">
-        <v>618</v>
-      </c>
       <c r="F20" s="24" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="G20" s="72" t="s">
         <v>302</v>
@@ -8535,22 +8534,22 @@
     </row>
     <row r="21" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A21" s="6" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="B21" s="6" t="s">
         <v>89</v>
       </c>
       <c r="C21" s="122" t="s">
+        <v>619</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>600</v>
+      </c>
+      <c r="E21" s="6" t="s">
         <v>620</v>
       </c>
-      <c r="D21" s="6" t="s">
-        <v>601</v>
-      </c>
-      <c r="E21" s="6" t="s">
-        <v>621</v>
-      </c>
       <c r="F21" s="24" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="G21" s="72" t="s">
         <v>302</v>
@@ -8559,22 +8558,22 @@
     </row>
     <row r="22" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A22" s="6" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="B22" s="6" t="s">
         <v>90</v>
       </c>
       <c r="C22" s="122" t="s">
+        <v>622</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>600</v>
+      </c>
+      <c r="E22" s="6" t="s">
         <v>623</v>
       </c>
-      <c r="D22" s="6" t="s">
-        <v>601</v>
-      </c>
-      <c r="E22" s="6" t="s">
-        <v>624</v>
-      </c>
       <c r="F22" s="24" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="G22" s="72" t="s">
         <v>302</v>
@@ -8583,22 +8582,22 @@
     </row>
     <row r="23" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A23" s="6" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>91</v>
       </c>
       <c r="C23" s="122" t="s">
+        <v>625</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>600</v>
+      </c>
+      <c r="E23" s="6" t="s">
         <v>626</v>
       </c>
-      <c r="D23" s="6" t="s">
-        <v>601</v>
-      </c>
-      <c r="E23" s="6" t="s">
-        <v>627</v>
-      </c>
       <c r="F23" s="24" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="G23" s="72" t="s">
         <v>302</v>
@@ -8607,22 +8606,22 @@
     </row>
     <row r="24" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A24" s="6" t="s">
+        <v>627</v>
+      </c>
+      <c r="B24" s="6" t="s">
         <v>628</v>
       </c>
-      <c r="B24" s="6" t="s">
+      <c r="C24" s="122" t="s">
         <v>629</v>
       </c>
-      <c r="C24" s="122" t="s">
+      <c r="D24" s="6" t="s">
+        <v>600</v>
+      </c>
+      <c r="E24" s="154" t="s">
         <v>630</v>
       </c>
-      <c r="D24" s="6" t="s">
-        <v>601</v>
-      </c>
-      <c r="E24" s="154" t="s">
-        <v>631</v>
-      </c>
       <c r="F24" s="24" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="G24" s="72" t="s">
         <v>302</v>
@@ -8631,22 +8630,22 @@
     </row>
     <row r="25" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A25" s="6" t="s">
+        <v>631</v>
+      </c>
+      <c r="B25" s="6" t="s">
         <v>632</v>
-      </c>
-      <c r="B25" s="6" t="s">
-        <v>633</v>
       </c>
       <c r="C25" s="122" t="s">
         <v>240</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="E25" s="154" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="F25" s="24" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="G25" s="72" t="s">
         <v>302</v>
@@ -8655,22 +8654,22 @@
     </row>
     <row r="26" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A26" s="6" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="B26" s="6" t="s">
         <v>92</v>
       </c>
       <c r="C26" s="122" t="s">
+        <v>635</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>600</v>
+      </c>
+      <c r="E26" s="6" t="s">
         <v>636</v>
       </c>
-      <c r="D26" s="6" t="s">
-        <v>601</v>
-      </c>
-      <c r="E26" s="6" t="s">
-        <v>637</v>
-      </c>
       <c r="F26" s="24" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="G26" s="72" t="s">
         <v>302</v>
@@ -8679,22 +8678,22 @@
     </row>
     <row r="27" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A27" s="6" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B27" s="6" t="s">
         <v>93</v>
       </c>
       <c r="C27" s="122" t="s">
+        <v>638</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>600</v>
+      </c>
+      <c r="E27" s="6" t="s">
         <v>639</v>
       </c>
-      <c r="D27" s="6" t="s">
-        <v>601</v>
-      </c>
-      <c r="E27" s="6" t="s">
-        <v>640</v>
-      </c>
       <c r="F27" s="24" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="G27" s="72" t="s">
         <v>302</v>
@@ -8703,22 +8702,22 @@
     </row>
     <row r="28" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A28" s="6" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="B28" s="6" t="s">
         <v>94</v>
       </c>
       <c r="C28" s="158" t="s">
+        <v>641</v>
+      </c>
+      <c r="D28" s="158" t="s">
         <v>642</v>
       </c>
-      <c r="D28" s="158" t="s">
+      <c r="E28" s="158" t="s">
         <v>643</v>
       </c>
-      <c r="E28" s="158" t="s">
-        <v>644</v>
-      </c>
       <c r="F28" s="163" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="G28" s="164" t="s">
         <v>302</v>
@@ -8727,18 +8726,18 @@
     </row>
     <row r="29" spans="1:8" s="35" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A29" s="6" t="s">
+        <v>644</v>
+      </c>
+      <c r="B29" s="168" t="s">
         <v>645</v>
       </c>
-      <c r="B29" s="168" t="s">
+      <c r="C29" s="168" t="s">
         <v>646</v>
-      </c>
-      <c r="C29" s="168" t="s">
-        <v>647</v>
       </c>
       <c r="D29" s="6"/>
       <c r="E29" s="157"/>
       <c r="F29" s="163" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="G29" s="164" t="s">
         <v>302</v>
@@ -8747,20 +8746,20 @@
     </row>
     <row r="30" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A30" s="6" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="B30" s="157" t="s">
         <v>95</v>
       </c>
       <c r="C30" s="66"/>
       <c r="D30" s="66" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="E30" s="66" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="F30" s="159" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="G30" s="160" t="s">
         <v>302</v>
@@ -8769,16 +8768,16 @@
     </row>
     <row r="31" spans="1:8" ht="29" x14ac:dyDescent="0.35">
       <c r="A31" s="6" t="s">
+        <v>649</v>
+      </c>
+      <c r="B31" s="162" t="s">
         <v>650</v>
-      </c>
-      <c r="B31" s="162" t="s">
-        <v>651</v>
       </c>
       <c r="C31" s="66"/>
       <c r="D31" s="66"/>
       <c r="E31" s="66"/>
       <c r="F31" s="165" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="G31" s="160" t="s">
         <v>302</v>
@@ -8787,7 +8786,7 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A32" s="6" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B32" s="162" t="s">
         <v>332</v>
@@ -8869,7 +8868,7 @@
     </row>
     <row r="2" spans="1:7" ht="45.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="206" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B2" s="206"/>
       <c r="C2" s="173"/>
@@ -8894,10 +8893,10 @@
         <v>295</v>
       </c>
       <c r="D4" s="75" t="s">
+        <v>654</v>
+      </c>
+      <c r="E4" s="75" t="s">
         <v>655</v>
-      </c>
-      <c r="E4" s="75" t="s">
-        <v>656</v>
       </c>
       <c r="F4" s="116" t="s">
         <v>297</v>
@@ -8934,7 +8933,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" s="21" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="B7" s="5"/>
       <c r="C7" s="5"/>
@@ -8986,7 +8985,7 @@
     </row>
     <row r="2" spans="1:7" ht="46.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="182" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="B2" s="182"/>
       <c r="C2" s="173"/>
@@ -9011,10 +9010,10 @@
         <v>295</v>
       </c>
       <c r="D4" s="75" t="s">
+        <v>654</v>
+      </c>
+      <c r="E4" s="75" t="s">
         <v>655</v>
-      </c>
-      <c r="E4" s="75" t="s">
-        <v>656</v>
       </c>
       <c r="F4" s="116" t="s">
         <v>297</v>
@@ -9025,7 +9024,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" s="44" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
@@ -9051,7 +9050,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" s="21" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="B7" s="5"/>
       <c r="C7" s="3"/>
@@ -14801,7 +14800,7 @@
       <c r="E11" s="6"/>
       <c r="F11" s="6"/>
       <c r="G11" s="23" t="s">
-        <v>363</v>
+        <v>660</v>
       </c>
       <c r="H11" s="8" t="s">
         <v>308</v>
@@ -14811,53 +14810,53 @@
     <row r="12" spans="1:12" x14ac:dyDescent="0.35">
       <c r="C12" s="1"/>
       <c r="K12" s="118" t="s">
+        <v>363</v>
+      </c>
+      <c r="L12" s="119" t="s">
         <v>364</v>
-      </c>
-      <c r="L12" s="119" t="s">
-        <v>365</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.35">
       <c r="K13" s="11" t="s">
+        <v>365</v>
+      </c>
+      <c r="L13" s="12" t="s">
         <v>366</v>
-      </c>
-      <c r="L13" s="12" t="s">
-        <v>367</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.35">
       <c r="K14" s="11"/>
       <c r="L14" s="12" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.35">
       <c r="K15" s="11"/>
       <c r="L15" s="12" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.35">
       <c r="K16" s="11"/>
       <c r="L16" s="12" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="17" spans="11:12" x14ac:dyDescent="0.35">
       <c r="K17" s="11"/>
       <c r="L17" s="12" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="18" spans="11:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="K18" s="13"/>
       <c r="L18" s="14" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="19" spans="11:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="K19" s="183" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="L19" s="184"/>
     </row>
@@ -14868,7 +14867,7 @@
       <selection sqref="A1:K1"/>
       <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
       <pageSetup orientation="portrait" r:id="rId1"/>
-      <autoFilter ref="A2:P11" xr:uid="{31D135D1-19CC-4FAC-B376-2E81581D0D4E}"/>
+      <autoFilter ref="A2:P11" xr:uid="{8E9FD0EC-7C93-4FFE-86EC-BEF41D1A6BF2}"/>
     </customSheetView>
   </customSheetViews>
   <mergeCells count="5">
@@ -14913,7 +14912,7 @@
     </row>
     <row r="2" spans="1:9" ht="18.649999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B2" s="187" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C2" s="188"/>
       <c r="D2" s="173"/>
@@ -14929,7 +14928,7 @@
     </row>
     <row r="4" spans="1:9" ht="18.649999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="181" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B4" s="181"/>
       <c r="C4" s="181"/>
@@ -14942,7 +14941,7 @@
     </row>
     <row r="5" spans="1:9" ht="33.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="185" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B5" s="186"/>
       <c r="C5" s="186"/>
@@ -14983,51 +14982,51 @@
     </row>
     <row r="7" spans="1:9" s="35" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A7" s="6" t="s">
+        <v>376</v>
+      </c>
+      <c r="B7" s="8" t="s">
         <v>377</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="C7" s="8" t="s">
         <v>378</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>379</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>235</v>
       </c>
       <c r="E7" s="6" t="s">
+        <v>379</v>
+      </c>
+      <c r="F7" s="6" t="s">
         <v>380</v>
       </c>
-      <c r="F7" s="6" t="s">
+      <c r="G7" s="8" t="s">
         <v>381</v>
-      </c>
-      <c r="G7" s="8" t="s">
-        <v>382</v>
       </c>
       <c r="H7" s="8" t="s">
         <v>308</v>
       </c>
       <c r="I7" s="74" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="8" spans="1:9" s="35" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A8" s="6" t="s">
+        <v>383</v>
+      </c>
+      <c r="B8" s="8" t="s">
         <v>384</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="C8" s="8" t="s">
         <v>385</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>386</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>235</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="G8" s="6" t="s">
         <v>312</v>
@@ -15039,25 +15038,25 @@
     </row>
     <row r="9" spans="1:9" s="35" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A9" s="6" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B9" s="131" t="s">
         <v>238</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>235</v>
       </c>
       <c r="E9" s="6" t="s">
+        <v>389</v>
+      </c>
+      <c r="F9" s="6" t="s">
         <v>390</v>
       </c>
-      <c r="F9" s="6" t="s">
+      <c r="G9" s="8" t="s">
         <v>391</v>
-      </c>
-      <c r="G9" s="8" t="s">
-        <v>392</v>
       </c>
       <c r="H9" s="8" t="s">
         <v>308</v>
@@ -15066,20 +15065,20 @@
     </row>
     <row r="10" spans="1:9" s="35" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A10" s="6" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B10" s="131" t="s">
         <v>183</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="D10" s="6"/>
       <c r="E10" s="6" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="G10" s="6" t="s">
         <v>312</v>
@@ -15091,13 +15090,13 @@
     </row>
     <row r="11" spans="1:9" s="35" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A11" s="6" t="s">
+        <v>395</v>
+      </c>
+      <c r="B11" s="131" t="s">
         <v>396</v>
       </c>
-      <c r="B11" s="131" t="s">
+      <c r="C11" s="6" t="s">
         <v>397</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>398</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>235</v>
@@ -15118,22 +15117,22 @@
     </row>
     <row r="12" spans="1:9" s="35" customFormat="1" ht="145" x14ac:dyDescent="0.35">
       <c r="A12" s="6" t="s">
+        <v>398</v>
+      </c>
+      <c r="B12" s="131" t="s">
         <v>399</v>
       </c>
-      <c r="B12" s="131" t="s">
+      <c r="C12" s="8" t="s">
         <v>400</v>
-      </c>
-      <c r="C12" s="8" t="s">
-        <v>401</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>235</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="G12" s="6" t="s">
         <v>312</v>
@@ -15145,20 +15144,20 @@
     </row>
     <row r="13" spans="1:9" s="35" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A13" s="6" t="s">
+        <v>402</v>
+      </c>
+      <c r="B13" s="131" t="s">
         <v>403</v>
-      </c>
-      <c r="B13" s="131" t="s">
-        <v>404</v>
       </c>
       <c r="C13" s="8"/>
       <c r="D13" s="6" t="s">
         <v>235</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="G13" s="6" t="s">
         <v>312</v>
@@ -15170,20 +15169,20 @@
     </row>
     <row r="14" spans="1:9" s="35" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A14" s="6" t="s">
+        <v>405</v>
+      </c>
+      <c r="B14" s="131" t="s">
         <v>406</v>
-      </c>
-      <c r="B14" s="131" t="s">
-        <v>407</v>
       </c>
       <c r="C14" s="8"/>
       <c r="D14" s="6" t="s">
         <v>235</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="G14" s="6" t="s">
         <v>312</v>
@@ -15195,7 +15194,7 @@
     </row>
     <row r="15" spans="1:9" s="35" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A15" s="6" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B15" s="131" t="s">
         <v>184</v>
@@ -15205,10 +15204,10 @@
         <v>235</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="F15" s="128" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="G15" s="6" t="s">
         <v>312</v>
@@ -15220,20 +15219,20 @@
     </row>
     <row r="16" spans="1:9" s="35" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A16" s="6" t="s">
+        <v>410</v>
+      </c>
+      <c r="B16" s="131" t="s">
         <v>411</v>
-      </c>
-      <c r="B16" s="131" t="s">
-        <v>412</v>
       </c>
       <c r="C16" s="8"/>
       <c r="D16" s="6" t="s">
         <v>235</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="F16" s="128" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="G16" s="6" t="s">
         <v>312</v>
@@ -15245,20 +15244,20 @@
     </row>
     <row r="17" spans="1:9" s="35" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A17" s="6" t="s">
+        <v>413</v>
+      </c>
+      <c r="B17" s="8" t="s">
         <v>414</v>
-      </c>
-      <c r="B17" s="8" t="s">
-        <v>415</v>
       </c>
       <c r="C17" s="8"/>
       <c r="D17" s="6" t="s">
         <v>235</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="G17" s="6" t="s">
         <v>312</v>
@@ -15270,20 +15269,20 @@
     </row>
     <row r="18" spans="1:9" s="35" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A18" s="6" t="s">
+        <v>416</v>
+      </c>
+      <c r="B18" s="8" t="s">
         <v>417</v>
-      </c>
-      <c r="B18" s="8" t="s">
-        <v>418</v>
       </c>
       <c r="C18" s="8"/>
       <c r="D18" s="6" t="s">
         <v>235</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="G18" s="6" t="s">
         <v>312</v>
@@ -15295,7 +15294,7 @@
     </row>
     <row r="19" spans="1:9" s="35" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A19" s="6" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B19" s="8" t="s">
         <v>185</v>
@@ -15305,10 +15304,10 @@
         <v>235</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G19" s="6" t="s">
         <v>312</v>
@@ -15320,20 +15319,20 @@
     </row>
     <row r="20" spans="1:9" s="35" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A20" s="6" t="s">
+        <v>421</v>
+      </c>
+      <c r="B20" s="8" t="s">
         <v>422</v>
-      </c>
-      <c r="B20" s="8" t="s">
-        <v>423</v>
       </c>
       <c r="C20" s="8"/>
       <c r="D20" s="6" t="s">
         <v>235</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="G20" s="6" t="s">
         <v>312</v>
@@ -15345,7 +15344,7 @@
     </row>
     <row r="21" spans="1:9" s="35" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A21" s="6" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B21" s="8" t="s">
         <v>76</v>
@@ -15355,10 +15354,10 @@
         <v>235</v>
       </c>
       <c r="E21" s="6" t="s">
+        <v>425</v>
+      </c>
+      <c r="F21" s="6" t="s">
         <v>426</v>
-      </c>
-      <c r="F21" s="6" t="s">
-        <v>427</v>
       </c>
       <c r="G21" s="6" t="s">
         <v>312</v>
@@ -15370,7 +15369,7 @@
     </row>
     <row r="22" spans="1:9" s="35" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A22" s="6" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="B22" s="8" t="s">
         <v>78</v>
@@ -15380,7 +15379,7 @@
         <v>235</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>347</v>
@@ -15395,7 +15394,7 @@
     </row>
     <row r="23" spans="1:9" s="35" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A23" s="6" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B23" s="8" t="s">
         <v>186</v>
@@ -15405,10 +15404,10 @@
         <v>235</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="G23" s="6" t="s">
         <v>312</v>
@@ -15420,20 +15419,20 @@
     </row>
     <row r="24" spans="1:9" s="35" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A24" s="6" t="s">
+        <v>431</v>
+      </c>
+      <c r="B24" s="8" t="s">
         <v>432</v>
-      </c>
-      <c r="B24" s="8" t="s">
-        <v>433</v>
       </c>
       <c r="C24" s="8"/>
       <c r="D24" s="6" t="s">
         <v>235</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="G24" s="6" t="s">
         <v>312</v>
@@ -15445,7 +15444,7 @@
     </row>
     <row r="25" spans="1:9" s="35" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A25" s="6" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B25" s="8" t="s">
         <v>187</v>
@@ -15455,10 +15454,10 @@
         <v>235</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="G25" s="6" t="s">
         <v>312</v>
@@ -15470,20 +15469,20 @@
     </row>
     <row r="26" spans="1:9" s="35" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A26" s="6" t="s">
+        <v>436</v>
+      </c>
+      <c r="B26" s="8" t="s">
         <v>437</v>
-      </c>
-      <c r="B26" s="8" t="s">
-        <v>438</v>
       </c>
       <c r="C26" s="8"/>
       <c r="D26" s="6" t="s">
         <v>235</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="G26" s="6" t="s">
         <v>312</v>
@@ -15495,7 +15494,7 @@
     </row>
     <row r="27" spans="1:9" s="35" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A27" s="6" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B27" s="8" t="s">
         <v>188</v>
@@ -15505,10 +15504,10 @@
         <v>235</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="F27" s="6" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="G27" s="6" t="s">
         <v>312</v>
@@ -15520,20 +15519,20 @@
     </row>
     <row r="28" spans="1:9" s="35" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A28" s="6" t="s">
+        <v>441</v>
+      </c>
+      <c r="B28" s="8" t="s">
         <v>442</v>
-      </c>
-      <c r="B28" s="8" t="s">
-        <v>443</v>
       </c>
       <c r="C28" s="8"/>
       <c r="D28" s="6" t="s">
         <v>235</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="F28" s="6" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="G28" s="6" t="s">
         <v>312</v>
@@ -15545,7 +15544,7 @@
     </row>
     <row r="29" spans="1:9" s="35" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A29" s="6" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="B29" s="8" t="s">
         <v>189</v>
@@ -15555,10 +15554,10 @@
         <v>235</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="F29" s="6" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="G29" s="6" t="s">
         <v>312</v>
@@ -15570,20 +15569,20 @@
     </row>
     <row r="30" spans="1:9" s="35" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A30" s="6" t="s">
+        <v>446</v>
+      </c>
+      <c r="B30" s="8" t="s">
         <v>447</v>
-      </c>
-      <c r="B30" s="8" t="s">
-        <v>448</v>
       </c>
       <c r="C30" s="8"/>
       <c r="D30" s="6" t="s">
         <v>235</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="F30" s="6" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="G30" s="6" t="s">
         <v>312</v>
@@ -15595,7 +15594,7 @@
     </row>
     <row r="31" spans="1:9" s="35" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A31" s="6" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B31" s="8" t="s">
         <v>190</v>
@@ -15605,10 +15604,10 @@
         <v>235</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="F31" s="6" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="G31" s="6" t="s">
         <v>312</v>
@@ -15620,20 +15619,20 @@
     </row>
     <row r="32" spans="1:9" s="35" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A32" s="6" t="s">
+        <v>451</v>
+      </c>
+      <c r="B32" s="8" t="s">
         <v>452</v>
-      </c>
-      <c r="B32" s="8" t="s">
-        <v>453</v>
       </c>
       <c r="C32" s="8"/>
       <c r="D32" s="6" t="s">
         <v>235</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="F32" s="6" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="G32" s="6" t="s">
         <v>312</v>
@@ -15645,20 +15644,20 @@
     </row>
     <row r="33" spans="1:9" s="35" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A33" s="6" t="s">
+        <v>454</v>
+      </c>
+      <c r="B33" s="8" t="s">
         <v>455</v>
-      </c>
-      <c r="B33" s="8" t="s">
-        <v>456</v>
       </c>
       <c r="C33" s="8"/>
       <c r="D33" s="6" t="s">
         <v>235</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="F33" s="6" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="G33" s="6" t="s">
         <v>312</v>
@@ -15727,7 +15726,7 @@
     </row>
     <row r="2" spans="1:7" ht="41.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="182" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B2" s="182"/>
       <c r="C2" s="170"/>
@@ -15771,22 +15770,22 @@
         <v>182</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C5" s="66" t="s">
         <v>235</v>
       </c>
       <c r="D5" s="66" t="s">
+        <v>458</v>
+      </c>
+      <c r="E5" s="67" t="s">
         <v>459</v>
       </c>
-      <c r="E5" s="67" t="s">
+      <c r="F5" s="58" t="s">
         <v>460</v>
       </c>
-      <c r="F5" s="58" t="s">
-        <v>461</v>
-      </c>
       <c r="G5" s="58" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -15794,22 +15793,22 @@
         <v>12</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="C6" s="66" t="s">
         <v>235</v>
       </c>
       <c r="D6" s="66" t="s">
+        <v>462</v>
+      </c>
+      <c r="E6" s="104" t="s">
         <v>463</v>
       </c>
-      <c r="E6" s="104" t="s">
-        <v>464</v>
-      </c>
       <c r="F6" s="58" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="G6" s="58" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="29" x14ac:dyDescent="0.35">
@@ -15823,24 +15822,24 @@
         <v>235</v>
       </c>
       <c r="D7" s="66" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="E7" s="104" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="F7" s="58" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="G7" s="58" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A8" s="8" t="s">
+        <v>465</v>
+      </c>
+      <c r="B8" s="8" t="s">
         <v>466</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>467</v>
       </c>
       <c r="C8" s="66" t="s">
         <v>235</v>
@@ -15849,13 +15848,13 @@
         <v>82</v>
       </c>
       <c r="E8" s="66" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="F8" s="58" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="G8" s="58" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="87" x14ac:dyDescent="0.35">
@@ -15863,7 +15862,7 @@
         <v>26</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C9" s="66"/>
       <c r="D9" s="66" t="s">
@@ -15873,10 +15872,10 @@
         <v>274</v>
       </c>
       <c r="F9" s="58" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="G9" s="58" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
   </sheetData>
@@ -15924,7 +15923,7 @@
     </row>
     <row r="2" spans="1:32" x14ac:dyDescent="0.35">
       <c r="B2" s="182" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="C2" s="182"/>
       <c r="D2" s="173"/>
@@ -15947,7 +15946,7 @@
     </row>
     <row r="5" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A5" s="181" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B5" s="181"/>
       <c r="C5" s="181"/>
@@ -15959,7 +15958,7 @@
     </row>
     <row r="6" spans="1:32" ht="41.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="186" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B6" s="186"/>
       <c r="C6" s="186"/>
@@ -15969,10 +15968,10 @@
       <c r="G6" s="186"/>
       <c r="H6" s="186"/>
       <c r="AA6" t="s">
+        <v>472</v>
+      </c>
+      <c r="AB6" s="192" t="s">
         <v>473</v>
-      </c>
-      <c r="AB6" s="192" t="s">
-        <v>474</v>
       </c>
       <c r="AC6" s="192"/>
       <c r="AD6" s="192"/>
@@ -16008,45 +16007,45 @@
         <v>167</v>
       </c>
       <c r="Y7" s="111" t="s">
+        <v>474</v>
+      </c>
+      <c r="Z7" s="111" t="s">
         <v>475</v>
       </c>
-      <c r="Z7" s="111" t="s">
+      <c r="AA7" s="64" t="s">
         <v>476</v>
       </c>
-      <c r="AA7" s="64" t="s">
+      <c r="AB7" s="64" t="s">
         <v>477</v>
       </c>
-      <c r="AB7" s="64" t="s">
+      <c r="AC7" s="64" t="s">
         <v>478</v>
       </c>
-      <c r="AC7" s="64" t="s">
+      <c r="AD7" s="64" t="s">
         <v>479</v>
-      </c>
-      <c r="AD7" s="64" t="s">
-        <v>480</v>
       </c>
     </row>
     <row r="8" spans="1:32" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A8" s="6" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B8" s="120" t="s">
         <v>174</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>235</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="F8" s="6" t="s">
         <v>276</v>
       </c>
       <c r="G8" s="24" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H8" s="24" t="s">
         <v>308</v>
@@ -16055,25 +16054,25 @@
     </row>
     <row r="9" spans="1:32" ht="29" x14ac:dyDescent="0.35">
       <c r="A9" s="6" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>238</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>235</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="F9" s="6" t="s">
         <v>43</v>
       </c>
       <c r="G9" s="24" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="H9" s="24" t="s">
         <v>308</v>
@@ -16082,13 +16081,13 @@
     </row>
     <row r="10" spans="1:32" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A10" s="6" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="B10" s="120" t="s">
         <v>254</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>235</v>
@@ -16100,34 +16099,34 @@
         <v>256</v>
       </c>
       <c r="G10" s="24" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="H10" s="24" t="s">
         <v>308</v>
       </c>
       <c r="I10" s="3"/>
       <c r="J10" s="115" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="11" spans="1:32" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A11" s="6" t="s">
+        <v>492</v>
+      </c>
+      <c r="B11" s="6" t="s">
         <v>493</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="C11" s="8" t="s">
         <v>494</v>
-      </c>
-      <c r="C11" s="8" t="s">
-        <v>495</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>235</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="G11" s="6" t="s">
         <v>312</v>
